--- a/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
+++ b/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
@@ -76,7 +76,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -108,8 +108,13 @@
         <fgColor rgb="00FFF7D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border/>
     <border/>
     <border>
@@ -172,11 +177,25 @@
         <color rgb="00E5E7EB"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D1D5DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D1D5DB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="199">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -635,6 +654,18 @@
     </xf>
     <xf numFmtId="165" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -2643,7 +2674,7 @@
       </s:c>
       <s:c r="C18" s="173">
         <s:f>'05_Annual_Model'!M24</s:f>
-        <s:v>6711160.0</s:v>
+        <s:v>6730600.0</s:v>
       </s:c>
       <s:c r="D18" s="173">
         <s:f>'05_Annual_Model'!M51</s:f>
@@ -2676,7 +2707,7 @@
       </s:c>
       <s:c r="C19" s="173">
         <s:f>'05_Annual_Model'!C25</s:f>
-        <s:v>2947410.4186040126</s:v>
+        <s:v>2959712.5361993117</s:v>
       </s:c>
       <s:c r="D19" s="173">
         <s:f>'05_Annual_Model'!C52</s:f>
@@ -2709,7 +2740,7 @@
       </s:c>
       <s:c r="C20" s="176">
         <s:f>'05_Annual_Model'!C26</s:f>
-        <s:v>0.2611609229291165</s:v>
+        <s:v>0.2618003333030041</s:v>
       </s:c>
       <s:c r="D20" s="176">
         <s:f>'05_Annual_Model'!C53</s:f>
@@ -2742,7 +2773,7 @@
       </s:c>
       <s:c r="C21" s="171">
         <s:f>'05_Annual_Model'!C27</s:f>
-        <s:v>2.8961292874498503</s:v>
+        <s:v>2.901621743798384</s:v>
       </s:c>
       <s:c r="D21" s="171">
         <s:f>'05_Annual_Model'!C54</s:f>
@@ -3040,1471 +3071,1639 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>通用输入假设｜能源托管 vs LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="18" t="n"/>
-      <c r="J1" s="18" t="n"/>
-      <c r="K1" s="18" t="n"/>
-      <c r="L1" s="18" t="n"/>
-      <c r="M1" s="18" t="n"/>
-      <c r="N1" s="18" t="n"/>
-      <c r="O1" s="18" t="n"/>
-      <c r="P1" s="18" t="n"/>
-      <c r="Q1" s="18" t="n"/>
-      <c r="R1" s="18" t="n"/>
-      <c r="S1" s="18" t="n"/>
-      <c r="T1" s="18" t="n"/>
-      <c r="U1" s="18" t="n"/>
-      <c r="V1" s="18" t="n"/>
-      <c r="W1" s="18" t="n"/>
-      <c r="X1" s="18" t="n"/>
-      <c r="Y1" s="18" t="n"/>
-      <c r="Z1" s="18" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>蓝色数字为可修改输入。所有成本均按“正数成本/支出”录入，净现金流采用显性减法，避免把成本当收入相加。</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>模块</t>
-        </is>
-      </c>
-      <c r="B4" s="44" t="inlineStr">
-        <is>
-          <t>参数</t>
-        </is>
-      </c>
-      <c r="C4" s="44" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="D4" s="44" t="inlineStr">
-        <is>
-          <t>输入值</t>
-        </is>
-      </c>
-      <c r="E4" s="44" t="inlineStr">
-        <is>
-          <t>来源/依据</t>
-        </is>
-      </c>
-      <c r="F4" s="44" t="inlineStr">
-        <is>
-          <t>是否常改</t>
-        </is>
-      </c>
-      <c r="G4" s="44" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="H4" s="44" t="inlineStr">
-        <is>
-          <t>校验</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>模型期</t>
-        </is>
-      </c>
-      <c r="C5" s="45" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D5" s="178" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="45" t="inlineStr">
-        <is>
-          <t>用户示例/通用模型</t>
-        </is>
-      </c>
-      <c r="F5" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G5" s="60" t="inlineStr">
-        <is>
-          <t>模板当前展开Y0-Y10；如需15年可继续扩展年度列。</t>
-        </is>
-      </c>
-      <c r="H5" s="60" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>灯具数量</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>盏</t>
-        </is>
-      </c>
-      <c r="D6" s="178" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E6" s="45" t="inlineStr">
-        <is>
-          <t>用户示例假设</t>
-        </is>
-      </c>
-      <c r="F6" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G6" s="60" t="inlineStr">
-        <is>
-          <t>用于计算总能耗、总运维费、总CAPEX。</t>
-        </is>
-      </c>
-      <c r="H6" s="60" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B7" s="45" t="inlineStr">
-        <is>
-          <t>业主年度服务费预算/付费上限</t>
-        </is>
-      </c>
-      <c r="C7" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D7" s="179" t="n">
-        <v>2342300</v>
-      </c>
-      <c r="E7" s="45" t="inlineStr">
-        <is>
-          <t>用户示例假设</t>
-        </is>
-      </c>
-      <c r="F7" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G7" s="60" t="inlineStr">
-        <is>
-          <t>这里是业主每年可支付给服务商的固定预算，不是业主一次性CAPEX。</t>
-        </is>
-      </c>
-      <c r="H7" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>电价</t>
-        </is>
-      </c>
-      <c r="C8" s="45" t="inlineStr">
-        <is>
-          <t>元/kWh</t>
-        </is>
-      </c>
-      <c r="D8" s="179" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="45" t="inlineStr">
-        <is>
-          <t>用户示例假设</t>
-        </is>
-      </c>
-      <c r="F8" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G8" s="60" t="inlineStr">
-        <is>
-          <t>如存在峰谷电价，可替换为加权平均电价。</t>
-        </is>
-      </c>
-      <c r="H8" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>现状单灯功率</t>
-        </is>
-      </c>
-      <c r="C9" s="45" t="inlineStr">
-        <is>
-          <t>W/盏</t>
-        </is>
-      </c>
-      <c r="D9" s="180" t="n">
-        <v>204.8318804483188</v>
-      </c>
-      <c r="E9" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需现场替换</t>
-        </is>
-      </c>
-      <c r="F9" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G9" s="60" t="inlineStr">
-        <is>
-          <t>用于估算现状年用电量。</t>
-        </is>
-      </c>
-      <c r="H9" s="60" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>每日亮灯小时</t>
-        </is>
-      </c>
-      <c r="C10" s="45" t="inlineStr">
-        <is>
-          <t>小时/天</t>
-        </is>
-      </c>
-      <c r="D10" s="178" t="n">
-        <v>11</v>
-      </c>
-      <c r="E10" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需现场替换</t>
-        </is>
-      </c>
-      <c r="F10" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G10" s="60" t="inlineStr">
-        <is>
-          <t>路灯常按10-12小时估算，具体按当地控制策略替换。</t>
-        </is>
-      </c>
-      <c r="H10" s="60" t="inlineStr">
-        <is>
-          <t>0-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>年运行天数</t>
-        </is>
-      </c>
-      <c r="C11" s="45" t="inlineStr">
-        <is>
-          <t>天/年</t>
-        </is>
-      </c>
-      <c r="D11" s="178" t="n">
-        <v>365</v>
-      </c>
-      <c r="E11" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F11" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G11" s="60" t="inlineStr">
-        <is>
-          <t>通常取365。</t>
-        </is>
-      </c>
-      <c r="H11" s="60" t="inlineStr">
-        <is>
-          <t>&gt;0</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="inlineStr">
-        <is>
-          <t>现状运维单价</t>
-        </is>
-      </c>
-      <c r="C12" s="45" t="inlineStr">
-        <is>
-          <t>元/盏/年</t>
-        </is>
-      </c>
-      <c r="D12" s="178" t="n">
-        <v>122</v>
-      </c>
-      <c r="E12" s="45" t="inlineStr">
-        <is>
-          <t>用户示例假设</t>
-        </is>
-      </c>
-      <c r="F12" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G12" s="60" t="inlineStr">
-        <is>
-          <t>业主现状运维支出。</t>
-        </is>
-      </c>
-      <c r="H12" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="inlineStr">
-        <is>
-          <t>折现率</t>
-        </is>
-      </c>
-      <c r="C13" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D13" s="181" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E13" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F13" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G13" s="60" t="inlineStr">
-        <is>
-          <t>用于服务商NPV，可按资金成本/项目风险调整。</t>
-        </is>
-      </c>
-      <c r="H13" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>电价年增长率</t>
-        </is>
-      </c>
-      <c r="C14" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D14" s="181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F14" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G14" s="60" t="inlineStr">
-        <is>
-          <t>若不确定，可先设为0。</t>
-        </is>
-      </c>
-      <c r="H14" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B15" s="45" t="inlineStr">
-        <is>
-          <t>服务商成本年增长率</t>
-        </is>
-      </c>
-      <c r="C15" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D15" s="181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F15" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>用于运维、平台、备件等成本年度增长。</t>
-        </is>
-      </c>
-      <c r="H15" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B16" s="45" t="inlineStr">
-        <is>
-          <t>服务费年增长率</t>
-        </is>
-      </c>
-      <c r="C16" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D16" s="181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F16" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G16" s="60" t="inlineStr">
-        <is>
-          <t>若合同约定服务费递增，可在此填写。</t>
-        </is>
-      </c>
-      <c r="H16" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="45" t="inlineStr">
-        <is>
-          <t>基础参数</t>
-        </is>
-      </c>
-      <c r="B17" s="45" t="inlineStr">
-        <is>
-          <t>业主保留管理成本</t>
-        </is>
-      </c>
-      <c r="C17" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D17" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F17" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G17" s="60" t="inlineStr">
-        <is>
-          <t>如业主仍保留少量监督、接口、验收等管理成本。</t>
-        </is>
-      </c>
-      <c r="H17" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="50" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B18" s="50" t="inlineStr">
-        <is>
-          <t>初始CAPEX单价</t>
-        </is>
-      </c>
-      <c r="C18" s="50" t="inlineStr">
-        <is>
-          <t>元/盏</t>
-        </is>
-      </c>
-      <c r="D18" s="182" t="n">
-        <v>707.88</v>
-      </c>
-      <c r="E18" s="50" t="inlineStr">
-        <is>
-          <t>模型默认假设，需报价替换</t>
-        </is>
-      </c>
-      <c r="F18" s="50" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G18" s="61" t="inlineStr">
-        <is>
-          <t>含灯具、施工、基础控制等；现金流Y0扣减。</t>
-        </is>
-      </c>
-      <c r="H18" s="61" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B19" s="45" t="inlineStr">
-        <is>
-          <t>固定服务费收入</t>
-        </is>
-      </c>
-      <c r="C19" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D19" s="179" t="n">
-        <v>1635056</v>
-      </c>
-      <c r="E19" s="45" t="inlineStr">
-        <is>
-          <t>默认等于业主年度预算</t>
-        </is>
-      </c>
-      <c r="F19" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G19" s="60" t="inlineStr">
-        <is>
-          <t>服务商每年从业主获得的固定服务费。</t>
-        </is>
-      </c>
-      <c r="H19" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B20" s="45" t="inlineStr">
-        <is>
-          <t>其他/第三方收入</t>
-        </is>
-      </c>
-      <c r="C20" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D20" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F20" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G20" s="60" t="inlineStr">
-        <is>
-          <t>如非业主支付的增值收入；不自动计入业主支出，避免双算。</t>
-        </is>
-      </c>
-      <c r="H20" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B21" s="45" t="inlineStr">
-        <is>
-          <t>综合节电率</t>
-        </is>
-      </c>
-      <c r="C21" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D21" s="181" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E21" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需项目测算替换</t>
-        </is>
-      </c>
-      <c r="F21" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G21" s="60" t="inlineStr">
-        <is>
-          <t>LED改造+基础控制后的综合节电率。</t>
-        </is>
-      </c>
-      <c r="H21" s="60" t="inlineStr">
-        <is>
-          <t>0-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B22" s="45" t="inlineStr">
-        <is>
-          <t>服务商运维现金成本</t>
-        </is>
-      </c>
-      <c r="C22" s="45" t="inlineStr">
-        <is>
-          <t>元/盏/年</t>
-        </is>
-      </c>
-      <c r="D22" s="179" t="n">
-        <v>81.33333333333333</v>
-      </c>
-      <c r="E22" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需报价替换</t>
-        </is>
-      </c>
-      <c r="F22" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G22" s="60" t="inlineStr">
-        <is>
-          <t>服务商实际维护成本，按正数录入。</t>
-        </is>
-      </c>
-      <c r="H22" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B23" s="45" t="inlineStr">
-        <is>
-          <t>平台/管理成本</t>
-        </is>
-      </c>
-      <c r="C23" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D23" s="179" t="n">
-        <v>152500</v>
-      </c>
-      <c r="E23" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F23" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G23" s="60" t="inlineStr">
-        <is>
-          <t>项目管理、平台接入、巡检系统等年度成本。</t>
-        </is>
-      </c>
-      <c r="H23" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B24" s="45" t="inlineStr">
-        <is>
-          <t>备件/小改造储备</t>
-        </is>
-      </c>
-      <c r="C24" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D24" s="179" t="n">
-        <v>50833.33333333333</v>
-      </c>
-      <c r="E24" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F24" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G24" s="60" t="inlineStr">
-        <is>
-          <t>备件更换、小修小改预留。</t>
-        </is>
-      </c>
-      <c r="H24" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B25" s="45" t="inlineStr">
-        <is>
-          <t>服务商是否承担电费</t>
-        </is>
-      </c>
-      <c r="C25" s="45" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="D25" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="45" t="inlineStr">
-        <is>
-          <t>模型开关</t>
-        </is>
-      </c>
-      <c r="F25" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G25" s="60" t="inlineStr">
-        <is>
-          <t>0=业主继续支付电费；1=服务商承担电费。</t>
-        </is>
-      </c>
-      <c r="H25" s="60" t="inlineStr">
-        <is>
-          <t>0或1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B26" s="45" t="inlineStr">
-        <is>
-          <t>资产转让年份</t>
-        </is>
-      </c>
-      <c r="C26" s="45" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D26" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F26" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G26" s="60" t="inlineStr">
-        <is>
-          <t>0表示不转让；如第5年转让则填5。</t>
-        </is>
-      </c>
-      <c r="H26" s="60" t="inlineStr">
-        <is>
-          <t>0-模型期</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="45" t="inlineStr">
-        <is>
-          <t>能源托管/EMC</t>
-        </is>
-      </c>
-      <c r="B27" s="45" t="inlineStr">
-        <is>
-          <t>资产转让收入</t>
-        </is>
-      </c>
-      <c r="C27" s="45" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D27" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F27" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G27" s="60" t="inlineStr">
-        <is>
-          <t>资产买断/转让收入；仅在资产转让年份进入服务商现金流。</t>
-        </is>
-      </c>
-      <c r="H27" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="50" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B28" s="50" t="inlineStr">
-        <is>
-          <t>初始CAPEX单价</t>
-        </is>
-      </c>
-      <c r="C28" s="50" t="inlineStr">
-        <is>
-          <t>元/盏</t>
-        </is>
-      </c>
-      <c r="D28" s="182" t="n">
-        <v>707.88</v>
-      </c>
-      <c r="E28" s="50" t="inlineStr">
-        <is>
-          <t>模型默认假设，需报价替换</t>
-        </is>
-      </c>
-      <c r="F28" s="50" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G28" s="61" t="inlineStr">
-        <is>
-          <t>通常含AI、通信、传感、平台接入，可能高于普通托管。</t>
-        </is>
-      </c>
-      <c r="H28" s="61" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B29" s="45" t="inlineStr">
-        <is>
-          <t>订阅费收入</t>
-        </is>
-      </c>
-      <c r="C29" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D29" s="179" t="n">
-        <v>2350000</v>
-      </c>
-      <c r="E29" s="45" t="inlineStr">
-        <is>
-          <t>默认等于业主年度预算</t>
-        </is>
-      </c>
-      <c r="F29" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G29" s="60" t="inlineStr">
-        <is>
-          <t>服务商每年从业主获得的订阅费。</t>
-        </is>
-      </c>
-      <c r="H29" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B30" s="45" t="inlineStr">
-        <is>
-          <t>其他/第三方收入</t>
-        </is>
-      </c>
-      <c r="C30" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D30" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F30" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G30" s="60" t="inlineStr">
-        <is>
-          <t>广告、数据服务、城市接口等收入；不自动计入业主支出。</t>
-        </is>
-      </c>
-      <c r="H30" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B31" s="45" t="inlineStr">
-        <is>
-          <t>综合节电率</t>
-        </is>
-      </c>
-      <c r="C31" s="45" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D31" s="181" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E31" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需项目测算替换</t>
-        </is>
-      </c>
-      <c r="F31" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G31" s="60" t="inlineStr">
-        <is>
-          <t>LED+AI调光+异常识别后的综合节电率。</t>
-        </is>
-      </c>
-      <c r="H31" s="60" t="inlineStr">
-        <is>
-          <t>0-95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B32" s="45" t="inlineStr">
-        <is>
-          <t>服务商运维现金成本</t>
-        </is>
-      </c>
-      <c r="C32" s="45" t="inlineStr">
-        <is>
-          <t>元/盏/年</t>
-        </is>
-      </c>
-      <c r="D32" s="179" t="n">
-        <v>18.42750000000001</v>
-      </c>
-      <c r="E32" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设，需项目测算替换</t>
-        </is>
-      </c>
-      <c r="F32" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G32" s="60" t="inlineStr">
-        <is>
-          <t>AI巡检、远程诊断、工单化后可能降低。</t>
-        </is>
-      </c>
-      <c r="H32" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B33" s="45" t="inlineStr">
-        <is>
-          <t>平台/AI升级成本</t>
-        </is>
-      </c>
-      <c r="C33" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D33" s="179" t="n">
-        <v>107493.75</v>
-      </c>
-      <c r="E33" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F33" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G33" s="60" t="inlineStr">
-        <is>
-          <t>算法、平台、通信、云资源、版本升级等年度成本。</t>
-        </is>
-      </c>
-      <c r="H33" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B34" s="45" t="inlineStr">
-        <is>
-          <t>升级/备件储备</t>
-        </is>
-      </c>
-      <c r="C34" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="D34" s="179" t="n">
-        <v>46068.75000000001</v>
-      </c>
-      <c r="E34" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F34" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G34" s="60" t="inlineStr">
-        <is>
-          <t>硬件升级、备件与系统迭代预留。</t>
-        </is>
-      </c>
-      <c r="H34" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B35" s="45" t="inlineStr">
-        <is>
-          <t>服务商是否承担电费</t>
-        </is>
-      </c>
-      <c r="C35" s="45" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
-      </c>
-      <c r="D35" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="45" t="inlineStr">
-        <is>
-          <t>模型开关</t>
-        </is>
-      </c>
-      <c r="F35" s="45" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="G35" s="60" t="inlineStr">
-        <is>
-          <t>0=业主继续支付电费；1=服务商承担电费。</t>
-        </is>
-      </c>
-      <c r="H35" s="60" t="inlineStr">
-        <is>
-          <t>0或1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B36" s="45" t="inlineStr">
-        <is>
-          <t>资产转让年份</t>
-        </is>
-      </c>
-      <c r="C36" s="45" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="D36" s="178" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F36" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G36" s="60" t="inlineStr">
-        <is>
-          <t>0表示不转让；如第5年转让则填5。</t>
-        </is>
-      </c>
-      <c r="H36" s="60" t="inlineStr">
-        <is>
-          <t>0-模型期</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="45" t="inlineStr">
-        <is>
-          <t>LaaS/AI订阅</t>
-        </is>
-      </c>
-      <c r="B37" s="45" t="inlineStr">
-        <is>
-          <t>资产转让收入</t>
-        </is>
-      </c>
-      <c r="C37" s="45" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="D37" s="179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="45" t="inlineStr">
-        <is>
-          <t>模型默认假设</t>
-        </is>
-      </c>
-      <c r="F37" s="45" t="inlineStr">
-        <is>
-          <t>可选</t>
-        </is>
-      </c>
-      <c r="G37" s="60" t="inlineStr">
-        <is>
-          <t>资产买断/转让收入；仅在资产转让年份进入服务商现金流。</t>
-        </is>
-      </c>
-      <c r="H37" s="60" t="inlineStr">
-        <is>
-          <t>&gt;=0</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>首期款(元)/客户预付</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>后4年年费减免(元/年)</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>方案标识</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Tier07_TailDiscount</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:sheetPr>
+    <s:outlinePr summaryBelow="1" summaryRight="1"/>
+    <s:pageSetUpPr/>
+  </s:sheetPr>
+  <s:dimension ref="A1:Z54"/>
+  <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <s:cols>
+    <s:col width="18" customWidth="1" min="1" max="1"/>
+    <s:col width="28" customWidth="1" min="2" max="2"/>
+    <s:col width="14" customWidth="1" min="3" max="3"/>
+    <s:col width="16" customWidth="1" min="4" max="4"/>
+    <s:col width="28" customWidth="1" min="5" max="5"/>
+    <s:col width="10" customWidth="1" min="6" max="6"/>
+    <s:col width="50" customWidth="1" min="7" max="7"/>
+    <s:col width="14" customWidth="1" min="8" max="8"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row r="1" ht="26" customHeight="1">
+      <s:c r="A1" s="5" t="inlineStr">
+        <s:is>
+          <s:t>通用输入假设｜能源托管 vs LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B1" s="1" t="n"/>
+      <s:c r="C1" s="1" t="n"/>
+      <s:c r="D1" s="1" t="n"/>
+      <s:c r="E1" s="1" t="n"/>
+      <s:c r="F1" s="1" t="n"/>
+      <s:c r="G1" s="1" t="n"/>
+      <s:c r="H1" s="1" t="n"/>
+      <s:c r="I1" s="18" t="n"/>
+      <s:c r="J1" s="18" t="n"/>
+      <s:c r="K1" s="18" t="n"/>
+      <s:c r="L1" s="18" t="n"/>
+      <s:c r="M1" s="18" t="n"/>
+      <s:c r="N1" s="18" t="n"/>
+      <s:c r="O1" s="18" t="n"/>
+      <s:c r="P1" s="18" t="n"/>
+      <s:c r="Q1" s="18" t="n"/>
+      <s:c r="R1" s="18" t="n"/>
+      <s:c r="S1" s="18" t="n"/>
+      <s:c r="T1" s="18" t="n"/>
+      <s:c r="U1" s="18" t="n"/>
+      <s:c r="V1" s="18" t="n"/>
+      <s:c r="W1" s="18" t="n"/>
+      <s:c r="X1" s="18" t="n"/>
+      <s:c r="Y1" s="18" t="n"/>
+      <s:c r="Z1" s="18" t="n"/>
+    </s:row>
+    <s:row r="2" ht="22" customHeight="1">
+      <s:c r="A2" s="7" t="inlineStr">
+        <s:is>
+          <s:t>蓝色数字为可修改输入。所有成本均按“正数成本/支出”录入，净现金流采用显性减法，避免把成本当收入相加。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B2" s="1" t="n"/>
+      <s:c r="C2" s="1" t="n"/>
+      <s:c r="D2" s="1" t="n"/>
+      <s:c r="E2" s="1" t="n"/>
+      <s:c r="F2" s="1" t="n"/>
+      <s:c r="G2" s="1" t="n"/>
+      <s:c r="H2" s="1" t="n"/>
+    </s:row>
+    <s:row r="4">
+      <s:c r="A4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>模块</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>单位</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>输入值</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>来源/依据</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>是否常改</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>备注</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>校验</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="5">
+      <s:c r="A5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型期</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D5" s="178" t="n">
+        <s:v>10</s:v>
+      </s:c>
+      <s:c r="E5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>用户示例/通用模型</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G5" s="60" t="inlineStr">
+        <s:is>
+          <s:t>模板当前展开Y0-Y10；如需15年可继续扩展年度列。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H5" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="6">
+      <s:c r="A6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>灯具数量</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D6" s="178" t="n">
+        <s:v>5000</s:v>
+      </s:c>
+      <s:c r="E6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>用户示例假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G6" s="60" t="inlineStr">
+        <s:is>
+          <s:t>用于计算总能耗、总运维费、总CAPEX。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H6" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="7">
+      <s:c r="A7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>业主年度服务费预算/付费上限</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D7" s="179" t="n">
+        <s:v>2342300</s:v>
+      </s:c>
+      <s:c r="E7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>用户示例假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G7" s="60" t="inlineStr">
+        <s:is>
+          <s:t>这里是业主每年可支付给服务商的固定预算，不是业主一次性CAPEX。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H7" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="8">
+      <s:c r="A8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>电价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/kWh</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D8" s="179" t="n">
+        <s:v>0.5</s:v>
+      </s:c>
+      <s:c r="E8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>用户示例假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G8" s="60" t="inlineStr">
+        <s:is>
+          <s:t>如存在峰谷电价，可替换为加权平均电价。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H8" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="9">
+      <s:c r="A9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>现状单灯功率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>W/盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D9" s="180" t="n">
+        <s:v>204.8318804483188</s:v>
+      </s:c>
+      <s:c r="E9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需现场替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G9" s="60" t="inlineStr">
+        <s:is>
+          <s:t>用于估算现状年用电量。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H9" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="10">
+      <s:c r="A10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>每日亮灯小时</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>小时/天</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D10" s="178" t="n">
+        <s:v>11</s:v>
+      </s:c>
+      <s:c r="E10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需现场替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G10" s="60" t="inlineStr">
+        <s:is>
+          <s:t>路灯常按10-12小时估算，具体按当地控制策略替换。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H10" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0-24</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="11">
+      <s:c r="A11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年运行天数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>天/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D11" s="178" t="n">
+        <s:v>365</s:v>
+      </s:c>
+      <s:c r="E11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G11" s="60" t="inlineStr">
+        <s:is>
+          <s:t>通常取365。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H11" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="12">
+      <s:c r="A12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>现状运维单价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/盏/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D12" s="178" t="n">
+        <s:v>122</s:v>
+      </s:c>
+      <s:c r="E12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>用户示例假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G12" s="60" t="inlineStr">
+        <s:is>
+          <s:t>业主现状运维支出。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H12" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="13">
+      <s:c r="A13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>折现率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D13" s="181" t="n">
+        <s:v>0.12</s:v>
+      </s:c>
+      <s:c r="E13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G13" s="60" t="inlineStr">
+        <s:is>
+          <s:t>用于服务商NPV，可按资金成本/项目风险调整。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H13" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="14">
+      <s:c r="A14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>电价年增长率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D14" s="181" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G14" s="60" t="inlineStr">
+        <s:is>
+          <s:t>若不确定，可先设为0。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H14" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="15">
+      <s:c r="A15" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B15" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务商成本年增长率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C15" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D15" s="181" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E15" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F15" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G15" s="60" t="inlineStr">
+        <s:is>
+          <s:t>用于运维、平台、备件等成本年度增长。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H15" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="16">
+      <s:c r="A16" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B16" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务费年增长率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C16" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D16" s="181" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E16" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F16" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G16" s="60" t="inlineStr">
+        <s:is>
+          <s:t>若合同约定服务费递增，可在此填写。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H16" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="17">
+      <s:c r="A17" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基础参数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B17" s="45" t="inlineStr">
+        <s:is>
+          <s:t>业主保留管理成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C17" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D17" s="179" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E17" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F17" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G17" s="60" t="inlineStr">
+        <s:is>
+          <s:t>如业主仍保留少量监督、接口、验收等管理成本。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H17" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="18">
+      <s:c r="A18" s="50" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B18" s="50" t="inlineStr">
+        <s:is>
+          <s:t>初始CAPEX单价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C18" s="50" t="inlineStr">
+        <s:is>
+          <s:t>元/盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D18" s="182" t="n">
+        <s:v>707.88</s:v>
+      </s:c>
+      <s:c r="E18" s="50" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需报价替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F18" s="50" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G18" s="61" t="inlineStr">
+        <s:is>
+          <s:t>含灯具、施工、基础控制等；现金流Y0扣减。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H18" s="61" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="19">
+      <s:c r="A19" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B19" s="45" t="inlineStr">
+        <s:is>
+          <s:t>固定服务费收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C19" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D19" s="179" t="n">
+        <s:v>1637000</s:v>
+      </s:c>
+      <s:c r="E19" s="45" t="inlineStr">
+        <s:is>
+          <s:t>默认等于业主年度预算</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F19" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G19" s="60" t="inlineStr">
+        <s:is>
+          <s:t>服务商每年从业主获得的固定服务费。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H19" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="20">
+      <s:c r="A20" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B20" s="45" t="inlineStr">
+        <s:is>
+          <s:t>其他/第三方收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C20" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D20" s="179" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E20" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F20" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G20" s="60" t="inlineStr">
+        <s:is>
+          <s:t>如非业主支付的增值收入；不自动计入业主支出，避免双算。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H20" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="21">
+      <s:c r="A21" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B21" s="45" t="inlineStr">
+        <s:is>
+          <s:t>综合节电率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C21" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D21" s="181" t="n">
+        <s:v>0.5</s:v>
+      </s:c>
+      <s:c r="E21" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需项目测算替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F21" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G21" s="60" t="inlineStr">
+        <s:is>
+          <s:t>LED改造+基础控制后的综合节电率。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H21" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0-95%</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="22">
+      <s:c r="A22" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B22" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务商运维现金成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C22" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/盏/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D22" s="179" t="n">
+        <s:v>81.33333333333333</s:v>
+      </s:c>
+      <s:c r="E22" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需报价替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F22" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G22" s="60" t="inlineStr">
+        <s:is>
+          <s:t>服务商实际维护成本，按正数录入。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H22" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="23">
+      <s:c r="A23" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B23" s="45" t="inlineStr">
+        <s:is>
+          <s:t>平台/管理成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C23" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D23" s="179" t="n">
+        <s:v>152500</s:v>
+      </s:c>
+      <s:c r="E23" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F23" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G23" s="60" t="inlineStr">
+        <s:is>
+          <s:t>项目管理、平台接入、巡检系统等年度成本。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H23" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="24">
+      <s:c r="A24" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B24" s="45" t="inlineStr">
+        <s:is>
+          <s:t>备件/小改造储备</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C24" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D24" s="179" t="n">
+        <s:v>50833.33333333333</s:v>
+      </s:c>
+      <s:c r="E24" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F24" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G24" s="60" t="inlineStr">
+        <s:is>
+          <s:t>备件更换、小修小改预留。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H24" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="25">
+      <s:c r="A25" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B25" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务商是否承担电费</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C25" s="45" t="inlineStr">
+        <s:is>
+          <s:t>0/1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D25" s="178" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E25" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型开关</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F25" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G25" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0=业主继续支付电费；1=服务商承担电费。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H25" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0或1</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="26">
+      <s:c r="A26" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B26" s="45" t="inlineStr">
+        <s:is>
+          <s:t>资产转让年份</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C26" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D26" s="178" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E26" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F26" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G26" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0表示不转让；如第5年转让则填5。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H26" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0-模型期</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="27">
+      <s:c r="A27" s="45" t="inlineStr">
+        <s:is>
+          <s:t>能源托管/EMC</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B27" s="45" t="inlineStr">
+        <s:is>
+          <s:t>资产转让收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C27" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D27" s="179" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E27" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F27" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G27" s="60" t="inlineStr">
+        <s:is>
+          <s:t>资产买断/转让收入；仅在资产转让年份进入服务商现金流。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H27" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="28">
+      <s:c r="A28" s="50" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B28" s="50" t="inlineStr">
+        <s:is>
+          <s:t>初始CAPEX单价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C28" s="50" t="inlineStr">
+        <s:is>
+          <s:t>元/盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D28" s="182">
+        <s:f>VLOOKUP($D$48,$A$52:$G$54,3,FALSE)</s:f>
+        <s:v>707.88</s:v>
+      </s:c>
+      <s:c r="E28" s="50" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需报价替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F28" s="50" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G28" s="61" t="inlineStr">
+        <s:is>
+          <s:t>通常含AI、通信、传感、平台接入，可能高于普通托管。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H28" s="61" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="29">
+      <s:c r="A29" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B29" s="45" t="inlineStr">
+        <s:is>
+          <s:t>订阅费收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C29" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D29" s="179" t="n">
+        <s:v>2350000</s:v>
+      </s:c>
+      <s:c r="E29" s="45" t="inlineStr">
+        <s:is>
+          <s:t>默认等于业主年度预算</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F29" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G29" s="60" t="inlineStr">
+        <s:is>
+          <s:t>服务商每年从业主获得的订阅费。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H29" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="30">
+      <s:c r="A30" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B30" s="45" t="inlineStr">
+        <s:is>
+          <s:t>其他/第三方收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C30" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D30" s="179" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E30" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F30" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G30" s="60" t="inlineStr">
+        <s:is>
+          <s:t>广告、数据服务、城市接口等收入；不自动计入业主支出。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H30" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="31">
+      <s:c r="A31" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B31" s="45" t="inlineStr">
+        <s:is>
+          <s:t>综合节电率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C31" s="45" t="inlineStr">
+        <s:is>
+          <s:t>%</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D31" s="181">
+        <s:f>MAX($D$21+0.03,VLOOKUP($D$48,$A$52:$G$54,2,FALSE))</s:f>
+        <s:v>0.85</s:v>
+      </s:c>
+      <s:c r="E31" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需项目测算替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F31" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G31" s="60" t="inlineStr">
+        <s:is>
+          <s:t>LED+AI调光+异常识别后的综合节电率。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H31" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0-95%</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="32">
+      <s:c r="A32" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B32" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务商运维现金成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C32" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/盏/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D32" s="179">
+        <s:f>VLOOKUP($D$48,$A$52:$G$54,4,FALSE)</s:f>
+        <s:v>18.427500000000002</s:v>
+      </s:c>
+      <s:c r="E32" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设，需项目测算替换</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F32" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G32" s="60" t="inlineStr">
+        <s:is>
+          <s:t>AI巡检、远程诊断、工单化后可能降低。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H32" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="33">
+      <s:c r="A33" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B33" s="45" t="inlineStr">
+        <s:is>
+          <s:t>平台/AI升级成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C33" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D33" s="179">
+        <s:f>VLOOKUP($D$48,$A$52:$G$54,5,FALSE)</s:f>
+        <s:v>107493.75000000003</s:v>
+      </s:c>
+      <s:c r="E33" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F33" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G33" s="60" t="inlineStr">
+        <s:is>
+          <s:t>算法、平台、通信、云资源、版本升级等年度成本。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H33" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="34">
+      <s:c r="A34" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B34" s="45" t="inlineStr">
+        <s:is>
+          <s:t>升级/备件储备</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C34" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D34" s="179">
+        <s:f>VLOOKUP($D$48,$A$52:$G$54,6,FALSE)</s:f>
+        <s:v>46068.75000000001</s:v>
+      </s:c>
+      <s:c r="E34" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F34" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G34" s="60" t="inlineStr">
+        <s:is>
+          <s:t>硬件升级、备件与系统迭代预留。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H34" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="35">
+      <s:c r="A35" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B35" s="45" t="inlineStr">
+        <s:is>
+          <s:t>服务商是否承担电费</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C35" s="45" t="inlineStr">
+        <s:is>
+          <s:t>0/1</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D35" s="178" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E35" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型开关</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F35" s="45" t="inlineStr">
+        <s:is>
+          <s:t>是</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G35" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0=业主继续支付电费；1=服务商承担电费。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H35" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0或1</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="36">
+      <s:c r="A36" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B36" s="45" t="inlineStr">
+        <s:is>
+          <s:t>资产转让年份</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C36" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D36" s="178" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E36" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F36" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G36" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0表示不转让；如第5年转让则填5。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H36" s="60" t="inlineStr">
+        <s:is>
+          <s:t>0-模型期</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="37">
+      <s:c r="A37" s="45" t="inlineStr">
+        <s:is>
+          <s:t>LaaS/AI订阅</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B37" s="45" t="inlineStr">
+        <s:is>
+          <s:t>资产转让收入</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C37" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D37" s="179" t="n">
+        <s:v>0</s:v>
+      </s:c>
+      <s:c r="E37" s="45" t="inlineStr">
+        <s:is>
+          <s:t>模型默认假设</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F37" s="45" t="inlineStr">
+        <s:is>
+          <s:t>可选</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G37" s="60" t="inlineStr">
+        <s:is>
+          <s:t>资产买断/转让收入；仅在资产转让年份进入服务商现金流。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="H37" s="60" t="inlineStr">
+        <s:is>
+          <s:t>&gt;=0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="44">
+      <s:c r="A44" s="183" t="inlineStr">
+        <s:is>
+          <s:t>商业条款/收费机制（可调整）</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B44" s="1" t="n"/>
+      <s:c r="C44" s="1" t="n"/>
+      <s:c r="D44" s="1" t="n"/>
+      <s:c r="E44" s="1" t="n"/>
+      <s:c r="F44" s="1" t="n"/>
+      <s:c r="G44" s="1" t="n"/>
+    </s:row>
+    <s:row r="45">
+      <s:c r="A45" t="inlineStr">
+        <s:is>
+          <s:t>首期款(元)/客户预付</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D45" t="n">
+        <s:v>0</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="46">
+      <s:c r="A46" t="inlineStr">
+        <s:is>
+          <s:t>后4年年费减免(元/年)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D46" t="n">
+        <s:v>250000</s:v>
+      </s:c>
+    </s:row>
+    <s:row r="47">
+      <s:c r="A47" t="inlineStr">
+        <s:is>
+          <s:t>方案标识</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D47" t="inlineStr">
+        <s:is>
+          <s:t>Tier07_TailDiscount</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="48">
+      <s:c r="A48" t="inlineStr">
+        <s:is>
+          <s:t>产品类型(product_key)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D48" t="inlineStr">
+        <s:is>
+          <s:t>AI_lightning_grid</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="50">
+      <s:c r="A50" s="183" t="inlineStr">
+        <s:is>
+          <s:t>产品对比（来自 defaults.py PRODUCT_ROWS；切换 D48 将联动 D28/D31/D32:D34）</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B50" s="1" t="n"/>
+      <s:c r="C50" s="1" t="n"/>
+      <s:c r="D50" s="1" t="n"/>
+      <s:c r="E50" s="1" t="n"/>
+      <s:c r="F50" s="1" t="n"/>
+      <s:c r="G50" s="1" t="n"/>
+    </s:row>
+    <s:row r="51">
+      <s:c r="A51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>产品(product_key)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>节电率下限(推导)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>LaaS CAPEX/盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>人工/维修(元/盏/年)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>平台费(元/年)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>备件(元/年)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G51" s="184" t="inlineStr">
+        <s:is>
+          <s:t>说明</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="52">
+      <s:c r="A52" s="185" t="inlineStr">
+        <s:is>
+          <s:t>AI_lightning_grid</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B52" s="186" t="n">
+        <s:v>0.5869565217391304</s:v>
+      </s:c>
+      <s:c r="C52" s="186" t="n">
+        <s:v>707.88</s:v>
+      </s:c>
+      <s:c r="D52" s="186" t="n">
+        <s:v>18.4275</s:v>
+      </s:c>
+      <s:c r="E52" s="186" t="n">
+        <s:v>107493.75</s:v>
+      </s:c>
+      <s:c r="F52" s="186" t="n">
+        <s:v>46068.75000000001</s:v>
+      </s:c>
+      <s:c r="G52" s="185" t="inlineStr">
+        <s:is>
+          <s:t>基础并网AI灯</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="53">
+      <s:c r="A53" s="185" t="inlineStr">
+        <s:is>
+          <s:t>AI_battery_integrated_grid</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B53" s="186" t="n">
+        <s:v>0.6458333333333333</s:v>
+      </s:c>
+      <s:c r="C53" s="186" t="n">
+        <s:v>775.9100259740259</s:v>
+      </s:c>
+      <s:c r="D53" s="186" t="n">
+        <s:v>17.855625</s:v>
+      </s:c>
+      <s:c r="E53" s="186" t="n">
+        <s:v>104157.8125</s:v>
+      </s:c>
+      <s:c r="F53" s="186" t="n">
+        <s:v>44639.06250000001</s:v>
+      </s:c>
+      <s:c r="G53" s="185" t="inlineStr">
+        <s:is>
+          <s:t>含电池：应急/出勤更少</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="54">
+      <s:c r="A54" s="185" t="inlineStr">
+        <s:is>
+          <s:t>AI_plus_solar_offgrid</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B54" s="186" t="n">
+        <s:v>0.999</s:v>
+      </s:c>
+      <s:c r="C54" s="186" t="n">
+        <s:v>671.1070129870129</s:v>
+      </s:c>
+      <s:c r="D54" s="186" t="n">
+        <s:v>5.718750000000001</s:v>
+      </s:c>
+      <s:c r="E54" s="186" t="n">
+        <s:v>33359.37500000001</s:v>
+      </s:c>
+      <s:c r="F54" s="186" t="n">
+        <s:v>14296.875</s:v>
+      </s:c>
+      <s:c r="G54" s="185" t="inlineStr">
+        <s:is>
+          <s:t>离网太阳能：电费≈0</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+  </s:sheetData>
+  <s:mergeCells count="4">
+    <s:mergeCell ref="A44:G44"/>
+    <s:mergeCell ref="A2:H2"/>
+    <s:mergeCell ref="A50:G50"/>
+    <s:mergeCell ref="A1:H1"/>
+  </s:mergeCells>
+  <s:dataValidations count="1">
+    <s:dataValidation sqref="D48" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="无效产品类型" error="请从下拉框选择：AI_lightning_grid / AI_battery_integrated_grid / AI_plus_solar_offgrid" promptTitle="产品类型(product_key)" prompt="用于区分不同产品的CAPEX/OPEX假设（来自 defaults.py PRODUCT_ROWS）。" type="list">
+      <s:formula1>"AI_lightning_grid,AI_battery_integrated_grid,AI_plus_solar_offgrid"</s:formula1>
+    </s:dataValidation>
+  </s:dataValidations>
+  <s:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</s:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4616,7 +4815,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D5" s="183">
+      <c r="D5" s="187">
         <f>'02_Inputs'!D6</f>
         <v/>
       </c>
@@ -4639,7 +4838,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D6" s="183">
+      <c r="D6" s="187">
         <f>'02_Inputs'!D9</f>
         <v/>
       </c>
@@ -4662,7 +4861,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D7" s="183">
+      <c r="D7" s="187">
         <f>'02_Inputs'!D10</f>
         <v/>
       </c>
@@ -4685,7 +4884,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D8" s="183">
+      <c r="D8" s="187">
         <f>'02_Inputs'!D11</f>
         <v/>
       </c>
@@ -4708,7 +4907,7 @@
           <t>每日亮灯小时×年运行天数</t>
         </is>
       </c>
-      <c r="D9" s="183">
+      <c r="D9" s="187">
         <f>D7*D8</f>
         <v/>
       </c>
@@ -4731,7 +4930,7 @@
           <t>灯具数量×单灯功率÷1000×年运行小时</t>
         </is>
       </c>
-      <c r="D10" s="183">
+      <c r="D10" s="187">
         <f>D5*D6/1000*D9</f>
         <v/>
       </c>
@@ -4754,7 +4953,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D11" s="184">
+      <c r="D11" s="188">
         <f>'02_Inputs'!D8</f>
         <v/>
       </c>
@@ -4777,7 +4976,7 @@
           <t>现状年用电量×电价</t>
         </is>
       </c>
-      <c r="D12" s="185">
+      <c r="D12" s="189">
         <f>D10*D11</f>
         <v/>
       </c>
@@ -4800,7 +4999,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D13" s="185">
+      <c r="D13" s="189">
         <f>'02_Inputs'!D12</f>
         <v/>
       </c>
@@ -4823,7 +5022,7 @@
           <t>灯具数量×现状运维单价</t>
         </is>
       </c>
-      <c r="D14" s="185">
+      <c r="D14" s="189">
         <f>D5*D13</f>
         <v/>
       </c>
@@ -4846,7 +5045,7 @@
           <t>基准年电费+基准年运维费</t>
         </is>
       </c>
-      <c r="D15" s="186">
+      <c r="D15" s="190">
         <f>D12+D14</f>
         <v/>
       </c>
@@ -4869,7 +5068,7 @@
           <t>来自Inputs</t>
         </is>
       </c>
-      <c r="D16" s="186">
+      <c r="D16" s="190">
         <f>'02_Inputs'!D7</f>
         <v/>
       </c>
@@ -4892,7 +5091,7 @@
           <t>年度预算×模型期</t>
         </is>
       </c>
-      <c r="D17" s="186">
+      <c r="D17" s="190">
         <f>D16*'02_Inputs'!D5</f>
         <v/>
       </c>
@@ -4915,7 +5114,7 @@
           <t>年度基准总成本合计，考虑增长率</t>
         </is>
       </c>
-      <c r="D18" s="186">
+      <c r="D18" s="190">
         <f>SUM('05_Annual_Model'!D8:M8)</f>
         <v/>
       </c>
@@ -5478,15 +5677,15 @@
           <t>元/年</t>
         </is>
       </c>
-      <c r="C16" s="187">
+      <c r="C16" s="191">
         <f>C6+C7</f>
         <v/>
       </c>
-      <c r="D16" s="187">
+      <c r="D16" s="191">
         <f>D6+D7</f>
         <v/>
       </c>
-      <c r="E16" s="187">
+      <c r="E16" s="191">
         <f>D16-C16</f>
         <v/>
       </c>
@@ -5517,15 +5716,15 @@
           <t>元/年</t>
         </is>
       </c>
-      <c r="C17" s="187">
+      <c r="C17" s="191">
         <f>C11+C13+C14+C15</f>
         <v/>
       </c>
-      <c r="D17" s="187">
+      <c r="D17" s="191">
         <f>D11+D13+D14+D15</f>
         <v/>
       </c>
-      <c r="E17" s="187">
+      <c r="E17" s="191">
         <f>C17-D17</f>
         <v/>
       </c>
@@ -5556,15 +5755,15 @@
           <t>元/年</t>
         </is>
       </c>
-      <c r="C18" s="187">
+      <c r="C18" s="191">
         <f>C16-C17</f>
         <v/>
       </c>
-      <c r="D18" s="187">
+      <c r="D18" s="191">
         <f>D16-D17</f>
         <v/>
       </c>
-      <c r="E18" s="187">
+      <c r="E18" s="191">
         <f>D18-C18</f>
         <v/>
       </c>
@@ -5595,15 +5794,15 @@
           <t>元/年</t>
         </is>
       </c>
-      <c r="C19" s="187">
+      <c r="C19" s="191">
         <f>C12+C6+'02_Inputs'!D17</f>
         <v/>
       </c>
-      <c r="D19" s="187">
+      <c r="D19" s="191">
         <f>D12+D6+'02_Inputs'!D17</f>
         <v/>
       </c>
-      <c r="E19" s="187">
+      <c r="E19" s="191">
         <f>C19-D19</f>
         <v/>
       </c>
@@ -5634,15 +5833,15 @@
           <t>元/年</t>
         </is>
       </c>
-      <c r="C20" s="187">
+      <c r="C20" s="191">
         <f>'03_Baseline'!D15-C19</f>
         <v/>
       </c>
-      <c r="D20" s="187">
+      <c r="D20" s="191">
         <f>'03_Baseline'!D15-D19</f>
         <v/>
       </c>
-      <c r="E20" s="187">
+      <c r="E20" s="191">
         <f>D20-C20</f>
         <v/>
       </c>
@@ -5673,15 +5872,15 @@
           <t>%</t>
         </is>
       </c>
-      <c r="C21" s="188">
+      <c r="C21" s="192">
         <f>C20/'03_Baseline'!D15</f>
         <v/>
       </c>
-      <c r="D21" s="188">
+      <c r="D21" s="192">
         <f>D20/'03_Baseline'!D15</f>
         <v/>
       </c>
-      <c r="E21" s="188">
+      <c r="E21" s="192">
         <f>D21-C21</f>
         <v/>
       </c>
@@ -5882,47 +6081,47 @@
           <s:t>基准年电费</s:t>
         </s:is>
       </s:c>
-      <s:c r="C6" s="189">
+      <s:c r="C6" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D6" s="189">
+      <s:c r="D6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E6" s="189">
+      <s:c r="E6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F6" s="189">
+      <s:c r="F6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G6" s="189">
+      <s:c r="G6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H6" s="189">
+      <s:c r="H6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I6" s="189">
+      <s:c r="I6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J6" s="189">
+      <s:c r="J6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K6" s="189">
+      <s:c r="K6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L6" s="189">
+      <s:c r="L6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M6" s="189">
+      <s:c r="M6" s="193">
         <s:f>'03_Baseline'!$D$12*(1+'02_Inputs'!$D$14)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -5938,47 +6137,47 @@
           <s:t>基准年运维费</s:t>
         </s:is>
       </s:c>
-      <s:c r="C7" s="189">
+      <s:c r="C7" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D7" s="189">
+      <s:c r="D7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E7" s="189">
+      <s:c r="E7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F7" s="189">
+      <s:c r="F7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G7" s="189">
+      <s:c r="G7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H7" s="189">
+      <s:c r="H7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I7" s="189">
+      <s:c r="I7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J7" s="189">
+      <s:c r="J7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K7" s="189">
+      <s:c r="K7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L7" s="189">
+      <s:c r="L7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M7" s="189">
+      <s:c r="M7" s="193">
         <s:f>'03_Baseline'!$D$14*(1+'02_Inputs'!$D$15)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -5994,47 +6193,47 @@
           <s:t>基准年总成本</s:t>
         </s:is>
       </s:c>
-      <s:c r="C8" s="189">
+      <s:c r="C8" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D8" s="189">
+      <s:c r="D8" s="193">
         <s:f>D6+D7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E8" s="189">
+      <s:c r="E8" s="193">
         <s:f>E6+E7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F8" s="189">
+      <s:c r="F8" s="193">
         <s:f>F6+F7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G8" s="189">
+      <s:c r="G8" s="193">
         <s:f>G6+G7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H8" s="189">
+      <s:c r="H8" s="193">
         <s:f>H6+H7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I8" s="189">
+      <s:c r="I8" s="193">
         <s:f>I6+I7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J8" s="189">
+      <s:c r="J8" s="193">
         <s:f>J6+J7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K8" s="189">
+      <s:c r="K8" s="193">
         <s:f>K6+K7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L8" s="189">
+      <s:c r="L8" s="193">
         <s:f>L6+L7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M8" s="189">
+      <s:c r="M8" s="193">
         <s:f>M6+M7</s:f>
         <s:v/>
       </s:c>
@@ -6050,47 +6249,47 @@
           <s:t>业主年度预算</s:t>
         </s:is>
       </s:c>
-      <s:c r="C9" s="189">
+      <s:c r="C9" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D9" s="189">
+      <s:c r="D9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E9" s="189">
+      <s:c r="E9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F9" s="189">
+      <s:c r="F9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G9" s="189">
+      <s:c r="G9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H9" s="189">
+      <s:c r="H9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I9" s="189">
+      <s:c r="I9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J9" s="189">
+      <s:c r="J9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K9" s="189">
+      <s:c r="K9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L9" s="189">
+      <s:c r="L9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M9" s="189">
+      <s:c r="M9" s="193">
         <s:f>'02_Inputs'!$D$7*(1+'02_Inputs'!$D$16)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -6098,17 +6297,17 @@
     <s:row r="10">
       <s:c r="A10" s="45" t="str"/>
       <s:c r="B10" s="45" t="str"/>
-      <s:c r="C10" s="189" t="n"/>
-      <s:c r="D10" s="189" t="n"/>
-      <s:c r="E10" s="189" t="n"/>
-      <s:c r="F10" s="189" t="n"/>
-      <s:c r="G10" s="189" t="n"/>
-      <s:c r="H10" s="189" t="n"/>
-      <s:c r="I10" s="189" t="n"/>
-      <s:c r="J10" s="189" t="n"/>
-      <s:c r="K10" s="189" t="n"/>
-      <s:c r="L10" s="189" t="n"/>
-      <s:c r="M10" s="189" t="n"/>
+      <s:c r="C10" s="193" t="n"/>
+      <s:c r="D10" s="193" t="n"/>
+      <s:c r="E10" s="193" t="n"/>
+      <s:c r="F10" s="193" t="n"/>
+      <s:c r="G10" s="193" t="n"/>
+      <s:c r="H10" s="193" t="n"/>
+      <s:c r="I10" s="193" t="n"/>
+      <s:c r="J10" s="193" t="n"/>
+      <s:c r="K10" s="193" t="n"/>
+      <s:c r="L10" s="193" t="n"/>
+      <s:c r="M10" s="193" t="n"/>
     </s:row>
     <s:row r="11">
       <s:c r="A11" s="50" t="inlineStr">
@@ -6117,17 +6316,17 @@
         </s:is>
       </s:c>
       <s:c r="B11" s="50" t="str"/>
-      <s:c r="C11" s="190" t="n"/>
-      <s:c r="D11" s="190" t="n"/>
-      <s:c r="E11" s="190" t="n"/>
-      <s:c r="F11" s="190" t="n"/>
-      <s:c r="G11" s="190" t="n"/>
-      <s:c r="H11" s="190" t="n"/>
-      <s:c r="I11" s="190" t="n"/>
-      <s:c r="J11" s="190" t="n"/>
-      <s:c r="K11" s="190" t="n"/>
-      <s:c r="L11" s="190" t="n"/>
-      <s:c r="M11" s="190" t="n"/>
+      <s:c r="C11" s="194" t="n"/>
+      <s:c r="D11" s="194" t="n"/>
+      <s:c r="E11" s="194" t="n"/>
+      <s:c r="F11" s="194" t="n"/>
+      <s:c r="G11" s="194" t="n"/>
+      <s:c r="H11" s="194" t="n"/>
+      <s:c r="I11" s="194" t="n"/>
+      <s:c r="J11" s="194" t="n"/>
+      <s:c r="K11" s="194" t="n"/>
+      <s:c r="L11" s="194" t="n"/>
+      <s:c r="M11" s="194" t="n"/>
     </s:row>
     <s:row r="12">
       <s:c r="A12" s="45" t="inlineStr">
@@ -6196,47 +6395,47 @@
           <s:t>固定服务费收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C13" s="189">
+      <s:c r="C13" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D13" s="189">
+      <s:c r="D13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E13" s="189">
+      <s:c r="E13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F13" s="189">
+      <s:c r="F13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G13" s="189">
+      <s:c r="G13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H13" s="189">
+      <s:c r="H13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I13" s="189">
+      <s:c r="I13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J13" s="189">
+      <s:c r="J13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K13" s="189">
+      <s:c r="K13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L13" s="189">
+      <s:c r="L13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M13" s="189">
+      <s:c r="M13" s="193">
         <s:f>'04_Mode_Params'!$C$6*(1+'02_Inputs'!$D$16)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -6252,47 +6451,47 @@
           <s:t>其他/第三方收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C14" s="189">
+      <s:c r="C14" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D14" s="189">
+      <s:c r="D14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E14" s="189">
+      <s:c r="E14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F14" s="189">
+      <s:c r="F14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G14" s="189">
+      <s:c r="G14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H14" s="189">
+      <s:c r="H14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I14" s="189">
+      <s:c r="I14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J14" s="189">
+      <s:c r="J14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K14" s="189">
+      <s:c r="K14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L14" s="189">
+      <s:c r="L14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M14" s="189">
+      <s:c r="M14" s="193">
         <s:f>'04_Mode_Params'!$C$7*(1+'02_Inputs'!$D$16)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -6308,47 +6507,47 @@
           <s:t>资产转让收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C15" s="189">
+      <s:c r="C15" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D15" s="189">
+      <s:c r="D15" s="193">
         <s:f>IF(AND(1='02_Inputs'!$D$26,1&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E15" s="189">
+      <s:c r="E15" s="193">
         <s:f>IF(AND(2='02_Inputs'!$D$26,2&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F15" s="189">
+      <s:c r="F15" s="193">
         <s:f>IF(AND(3='02_Inputs'!$D$26,3&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G15" s="189">
+      <s:c r="G15" s="193">
         <s:f>IF(AND(4='02_Inputs'!$D$26,4&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H15" s="189">
+      <s:c r="H15" s="193">
         <s:f>IF(AND(5='02_Inputs'!$D$26,5&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I15" s="189">
+      <s:c r="I15" s="193">
         <s:f>IF(AND(6='02_Inputs'!$D$26,6&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J15" s="189">
+      <s:c r="J15" s="193">
         <s:f>IF(AND(7='02_Inputs'!$D$26,7&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K15" s="189">
+      <s:c r="K15" s="193">
         <s:f>IF(AND(8='02_Inputs'!$D$26,8&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L15" s="189">
+      <s:c r="L15" s="193">
         <s:f>IF(AND(9='02_Inputs'!$D$26,9&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M15" s="189">
+      <s:c r="M15" s="193">
         <s:f>IF(AND(10='02_Inputs'!$D$26,10&gt;0),'02_Inputs'!$D$27,0)</s:f>
         <s:v/>
       </s:c>
@@ -6364,47 +6563,47 @@
           <s:t>节电后电费总额</s:t>
         </s:is>
       </s:c>
-      <s:c r="C16" s="189">
+      <s:c r="C16" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D16" s="189">
+      <s:c r="D16" s="193">
         <s:f>D6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E16" s="189">
+      <s:c r="E16" s="193">
         <s:f>E6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F16" s="189">
+      <s:c r="F16" s="193">
         <s:f>F6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G16" s="189">
+      <s:c r="G16" s="193">
         <s:f>G6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H16" s="189">
+      <s:c r="H16" s="193">
         <s:f>H6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I16" s="189">
+      <s:c r="I16" s="193">
         <s:f>I6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J16" s="189">
+      <s:c r="J16" s="193">
         <s:f>J6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K16" s="189">
+      <s:c r="K16" s="193">
         <s:f>K6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L16" s="189">
+      <s:c r="L16" s="193">
         <s:f>L6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M16" s="189">
+      <s:c r="M16" s="193">
         <s:f>M6*(1-'04_Mode_Params'!$C$8)</s:f>
         <s:v/>
       </s:c>
@@ -6644,47 +6843,47 @@
           <s:t>年度总收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C21" s="191">
+      <s:c r="C21" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D21" s="191">
+      <s:c r="D21" s="195">
         <s:f>D13+D14+D15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E21" s="191">
+      <s:c r="E21" s="195">
         <s:f>E13+E14+E15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F21" s="191">
+      <s:c r="F21" s="195">
         <s:f>F13+F14+F15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G21" s="191">
+      <s:c r="G21" s="195">
         <s:f>G13+G14+G15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H21" s="191">
+      <s:c r="H21" s="195">
         <s:f>H13+H14+H15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I21" s="191">
+      <s:c r="I21" s="195">
         <s:f>I13+I14+I15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J21" s="191">
+      <s:c r="J21" s="195">
         <s:f>J13+J14+J15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K21" s="191">
+      <s:c r="K21" s="195">
         <s:f>K13+K14+K15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L21" s="191">
+      <s:c r="L21" s="195">
         <s:f>L13+L14+L15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M21" s="191">
+      <s:c r="M21" s="195">
         <s:f>M13+M14+M15</s:f>
         <s:v/>
       </s:c>
@@ -6700,47 +6899,47 @@
           <s:t>年度总现金成本</s:t>
         </s:is>
       </s:c>
-      <s:c r="C22" s="191">
+      <s:c r="C22" s="195">
         <s:f>C12</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D22" s="191">
+      <s:c r="D22" s="195">
         <s:f>D12+D17+D18+D19+D20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E22" s="191">
+      <s:c r="E22" s="195">
         <s:f>E12+E17+E18+E19+E20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F22" s="191">
+      <s:c r="F22" s="195">
         <s:f>F12+F17+F18+F19+F20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G22" s="191">
+      <s:c r="G22" s="195">
         <s:f>G12+G17+G18+G19+G20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H22" s="191">
+      <s:c r="H22" s="195">
         <s:f>H12+H17+H18+H19+H20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I22" s="191">
+      <s:c r="I22" s="195">
         <s:f>I12+I17+I18+I19+I20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J22" s="191">
+      <s:c r="J22" s="195">
         <s:f>J12+J17+J18+J19+J20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K22" s="191">
+      <s:c r="K22" s="195">
         <s:f>K12+K17+K18+K19+K20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L22" s="191">
+      <s:c r="L22" s="195">
         <s:f>L12+L17+L18+L19+L20</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M22" s="191">
+      <s:c r="M22" s="195">
         <s:f>M12+M17+M18+M19+M20</s:f>
         <s:v/>
       </s:c>
@@ -6756,47 +6955,47 @@
           <s:t>年度净现金流</s:t>
         </s:is>
       </s:c>
-      <s:c r="C23" s="191">
+      <s:c r="C23" s="195">
         <s:f>C21-C22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D23" s="191">
+      <s:c r="D23" s="195">
         <s:f>D21-D22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E23" s="191">
+      <s:c r="E23" s="195">
         <s:f>E21-E22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F23" s="191">
+      <s:c r="F23" s="195">
         <s:f>F21-F22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G23" s="191">
+      <s:c r="G23" s="195">
         <s:f>G21-G22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H23" s="191">
+      <s:c r="H23" s="195">
         <s:f>H21-H22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I23" s="191">
+      <s:c r="I23" s="195">
         <s:f>I21-I22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J23" s="191">
+      <s:c r="J23" s="195">
         <s:f>J21-J22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K23" s="191">
+      <s:c r="K23" s="195">
         <s:f>K21-K22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L23" s="191">
+      <s:c r="L23" s="195">
         <s:f>L21-L22</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M23" s="191">
+      <s:c r="M23" s="195">
         <s:f>M21-M22</s:f>
         <s:v/>
       </s:c>
@@ -6812,49 +7011,49 @@
           <s:t>累计现金流</s:t>
         </s:is>
       </s:c>
-      <s:c r="C24" s="191">
+      <s:c r="C24" s="195">
         <s:f>C23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D24" s="191">
+      <s:c r="D24" s="195">
         <s:f>C24+D23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E24" s="191">
+      <s:c r="E24" s="195">
         <s:f>D24+E23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F24" s="191">
+      <s:c r="F24" s="195">
         <s:f>E24+F23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G24" s="191">
+      <s:c r="G24" s="195">
         <s:f>F24+G23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H24" s="191">
+      <s:c r="H24" s="195">
         <s:f>G24+H23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I24" s="191">
+      <s:c r="I24" s="195">
         <s:f>H24+I23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J24" s="191">
+      <s:c r="J24" s="195">
         <s:f>I24+J23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K24" s="191">
+      <s:c r="K24" s="195">
         <s:f>J24+K23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L24" s="191">
+      <s:c r="L24" s="195">
         <s:f>K24+L23</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M24" s="191">
+      <s:c r="M24" s="195">
         <s:f>L24+M23</s:f>
-        <s:v>6711160.0</s:v>
+        <s:v>6730600.0</s:v>
       </s:c>
     </s:row>
     <s:row r="25">
@@ -6868,20 +7067,20 @@
           <s:t>NPV</s:t>
         </s:is>
       </s:c>
-      <s:c r="C25" s="192">
+      <s:c r="C25" s="196">
         <s:f>NPV('02_Inputs'!$D$13,D23:M23)+C23</s:f>
-        <s:v>2947410.4186040126</s:v>
-      </s:c>
-      <s:c r="D25" s="189" t="n"/>
-      <s:c r="E25" s="189" t="n"/>
-      <s:c r="F25" s="189" t="n"/>
-      <s:c r="G25" s="189" t="n"/>
-      <s:c r="H25" s="189" t="n"/>
-      <s:c r="I25" s="189" t="n"/>
-      <s:c r="J25" s="189" t="n"/>
-      <s:c r="K25" s="189" t="n"/>
-      <s:c r="L25" s="189" t="n"/>
-      <s:c r="M25" s="189" t="n"/>
+        <s:v>2959712.5361993117</s:v>
+      </s:c>
+      <s:c r="D25" s="193" t="n"/>
+      <s:c r="E25" s="193" t="n"/>
+      <s:c r="F25" s="193" t="n"/>
+      <s:c r="G25" s="193" t="n"/>
+      <s:c r="H25" s="193" t="n"/>
+      <s:c r="I25" s="193" t="n"/>
+      <s:c r="J25" s="193" t="n"/>
+      <s:c r="K25" s="193" t="n"/>
+      <s:c r="L25" s="193" t="n"/>
+      <s:c r="M25" s="193" t="n"/>
     </s:row>
     <s:row r="26">
       <s:c r="A26" s="45" t="inlineStr">
@@ -6894,20 +7093,20 @@
           <s:t>IRR</s:t>
         </s:is>
       </s:c>
-      <s:c r="C26" s="193">
+      <s:c r="C26" s="197">
         <s:f>IFERROR(IRR(C23:M23),"n/a")</s:f>
-        <s:v>0.2611609229291165</s:v>
-      </s:c>
-      <s:c r="D26" s="194" t="n"/>
-      <s:c r="E26" s="194" t="n"/>
-      <s:c r="F26" s="194" t="n"/>
-      <s:c r="G26" s="194" t="n"/>
-      <s:c r="H26" s="194" t="n"/>
-      <s:c r="I26" s="194" t="n"/>
-      <s:c r="J26" s="194" t="n"/>
-      <s:c r="K26" s="194" t="n"/>
-      <s:c r="L26" s="194" t="n"/>
-      <s:c r="M26" s="194" t="n"/>
+        <s:v>0.2618003333030041</s:v>
+      </s:c>
+      <s:c r="D26" s="198" t="n"/>
+      <s:c r="E26" s="198" t="n"/>
+      <s:c r="F26" s="198" t="n"/>
+      <s:c r="G26" s="198" t="n"/>
+      <s:c r="H26" s="198" t="n"/>
+      <s:c r="I26" s="198" t="n"/>
+      <s:c r="J26" s="198" t="n"/>
+      <s:c r="K26" s="198" t="n"/>
+      <s:c r="L26" s="198" t="n"/>
+      <s:c r="M26" s="198" t="n"/>
     </s:row>
     <s:row r="27">
       <s:c r="A27" s="45" t="inlineStr">
@@ -6920,20 +7119,20 @@
           <s:t>10年ROI</s:t>
         </s:is>
       </s:c>
-      <s:c r="C27" s="195">
+      <s:c r="C27" s="199">
         <s:f>IF(C12=0,"n/a",SUM(C23:M23)/C12)</s:f>
-        <s:v>2.8961292874498503</s:v>
-      </s:c>
-      <s:c r="D27" s="194" t="n"/>
-      <s:c r="E27" s="194" t="n"/>
-      <s:c r="F27" s="194" t="n"/>
-      <s:c r="G27" s="194" t="n"/>
-      <s:c r="H27" s="194" t="n"/>
-      <s:c r="I27" s="194" t="n"/>
-      <s:c r="J27" s="194" t="n"/>
-      <s:c r="K27" s="194" t="n"/>
-      <s:c r="L27" s="194" t="n"/>
-      <s:c r="M27" s="194" t="n"/>
+        <s:v>2.901621743798384</s:v>
+      </s:c>
+      <s:c r="D27" s="198" t="n"/>
+      <s:c r="E27" s="198" t="n"/>
+      <s:c r="F27" s="198" t="n"/>
+      <s:c r="G27" s="198" t="n"/>
+      <s:c r="H27" s="198" t="n"/>
+      <s:c r="I27" s="198" t="n"/>
+      <s:c r="J27" s="198" t="n"/>
+      <s:c r="K27" s="198" t="n"/>
+      <s:c r="L27" s="198" t="n"/>
+      <s:c r="M27" s="198" t="n"/>
     </s:row>
     <s:row r="28">
       <s:c r="A28" s="45" t="inlineStr">
@@ -6946,35 +7145,35 @@
           <s:t>静态回收期</s:t>
         </s:is>
       </s:c>
-      <s:c r="C28" s="196">
+      <s:c r="C28" s="200">
         <s:f>IF(M24&lt;0,"未回收",IF(C24&gt;=0,C$4,IF(D24&gt;=0,D$4,IF(E24&gt;=0,E$4,IF(F24&gt;=0,F$4,IF(G24&gt;=0,G$4,IF(H24&gt;=0,H$4,IF(I24&gt;=0,I$4,IF(J24&gt;=0,J$4,IF(K24&gt;=0,K$4,IF(L24&gt;=0,L$4,M$4)))))))))))</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D28" s="197" t="n"/>
-      <s:c r="E28" s="197" t="n"/>
-      <s:c r="F28" s="197" t="n"/>
-      <s:c r="G28" s="197" t="n"/>
-      <s:c r="H28" s="197" t="n"/>
-      <s:c r="I28" s="197" t="n"/>
-      <s:c r="J28" s="197" t="n"/>
-      <s:c r="K28" s="197" t="n"/>
-      <s:c r="L28" s="197" t="n"/>
-      <s:c r="M28" s="197" t="n"/>
+      <s:c r="D28" s="201" t="n"/>
+      <s:c r="E28" s="201" t="n"/>
+      <s:c r="F28" s="201" t="n"/>
+      <s:c r="G28" s="201" t="n"/>
+      <s:c r="H28" s="201" t="n"/>
+      <s:c r="I28" s="201" t="n"/>
+      <s:c r="J28" s="201" t="n"/>
+      <s:c r="K28" s="201" t="n"/>
+      <s:c r="L28" s="201" t="n"/>
+      <s:c r="M28" s="201" t="n"/>
     </s:row>
     <s:row r="29">
       <s:c r="A29" s="45" t="str"/>
       <s:c r="B29" s="45" t="str"/>
-      <s:c r="C29" s="189" t="n"/>
-      <s:c r="D29" s="189" t="n"/>
-      <s:c r="E29" s="189" t="n"/>
-      <s:c r="F29" s="189" t="n"/>
-      <s:c r="G29" s="189" t="n"/>
-      <s:c r="H29" s="189" t="n"/>
-      <s:c r="I29" s="189" t="n"/>
-      <s:c r="J29" s="189" t="n"/>
-      <s:c r="K29" s="189" t="n"/>
-      <s:c r="L29" s="189" t="n"/>
-      <s:c r="M29" s="189" t="n"/>
+      <s:c r="C29" s="193" t="n"/>
+      <s:c r="D29" s="193" t="n"/>
+      <s:c r="E29" s="193" t="n"/>
+      <s:c r="F29" s="193" t="n"/>
+      <s:c r="G29" s="193" t="n"/>
+      <s:c r="H29" s="193" t="n"/>
+      <s:c r="I29" s="193" t="n"/>
+      <s:c r="J29" s="193" t="n"/>
+      <s:c r="K29" s="193" t="n"/>
+      <s:c r="L29" s="193" t="n"/>
+      <s:c r="M29" s="193" t="n"/>
     </s:row>
     <s:row r="30">
       <s:c r="A30" s="50" t="inlineStr">
@@ -6983,17 +7182,17 @@
         </s:is>
       </s:c>
       <s:c r="B30" s="50" t="str"/>
-      <s:c r="C30" s="190" t="n"/>
-      <s:c r="D30" s="190" t="n"/>
-      <s:c r="E30" s="190" t="n"/>
-      <s:c r="F30" s="190" t="n"/>
-      <s:c r="G30" s="190" t="n"/>
-      <s:c r="H30" s="190" t="n"/>
-      <s:c r="I30" s="190" t="n"/>
-      <s:c r="J30" s="190" t="n"/>
-      <s:c r="K30" s="190" t="n"/>
-      <s:c r="L30" s="190" t="n"/>
-      <s:c r="M30" s="190" t="n"/>
+      <s:c r="C30" s="194" t="n"/>
+      <s:c r="D30" s="194" t="n"/>
+      <s:c r="E30" s="194" t="n"/>
+      <s:c r="F30" s="194" t="n"/>
+      <s:c r="G30" s="194" t="n"/>
+      <s:c r="H30" s="194" t="n"/>
+      <s:c r="I30" s="194" t="n"/>
+      <s:c r="J30" s="194" t="n"/>
+      <s:c r="K30" s="194" t="n"/>
+      <s:c r="L30" s="194" t="n"/>
+      <s:c r="M30" s="194" t="n"/>
     </s:row>
     <s:row r="31">
       <s:c r="A31" s="45" t="inlineStr">
@@ -7006,47 +7205,47 @@
           <s:t>业主支付电费</s:t>
         </s:is>
       </s:c>
-      <s:c r="C31" s="189">
+      <s:c r="C31" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D31" s="189">
+      <s:c r="D31" s="193">
         <s:f>D16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="E31" s="189">
+      <s:c r="E31" s="193">
         <s:f>E16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="F31" s="189">
+      <s:c r="F31" s="193">
         <s:f>F16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="G31" s="189">
+      <s:c r="G31" s="193">
         <s:f>G16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="H31" s="189">
+      <s:c r="H31" s="193">
         <s:f>H16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="I31" s="189">
+      <s:c r="I31" s="193">
         <s:f>I16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="J31" s="189">
+      <s:c r="J31" s="193">
         <s:f>J16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="K31" s="189">
+      <s:c r="K31" s="193">
         <s:f>K16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="L31" s="189">
+      <s:c r="L31" s="193">
         <s:f>L16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
-      <s:c r="M31" s="189">
+      <s:c r="M31" s="193">
         <s:f>M16*(1-'04_Mode_Params'!$C$10)</s:f>
         <s:v>1028000.0</s:v>
       </s:c>
@@ -7062,49 +7261,49 @@
           <s:t>固定服务费支出</s:t>
         </s:is>
       </s:c>
-      <s:c r="C32" s="189">
+      <s:c r="C32" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D32" s="189">
+      <s:c r="D32" s="193">
         <s:f>D13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="E32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="E32" s="193">
         <s:f>E13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="F32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="F32" s="193">
         <s:f>F13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="G32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="G32" s="193">
         <s:f>G13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="H32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="H32" s="193">
         <s:f>H13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="I32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="I32" s="193">
         <s:f>I13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="J32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="J32" s="193">
         <s:f>J13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="K32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="K32" s="193">
         <s:f>K13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="L32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="L32" s="193">
         <s:f>L13</s:f>
-        <s:v>1635056.0</s:v>
-      </s:c>
-      <s:c r="M32" s="189">
+        <s:v>1637000.0</s:v>
+      </s:c>
+      <s:c r="M32" s="193">
         <s:f>M13</s:f>
-        <s:v>1635056.0</s:v>
+        <s:v>1637000.0</s:v>
       </s:c>
     </s:row>
     <s:row r="33">
@@ -7118,47 +7317,47 @@
           <s:t>业主保留管理成本</s:t>
         </s:is>
       </s:c>
-      <s:c r="C33" s="189">
+      <s:c r="C33" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D33" s="189">
+      <s:c r="D33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E33" s="189">
+      <s:c r="E33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F33" s="189">
+      <s:c r="F33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G33" s="189">
+      <s:c r="G33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H33" s="189">
+      <s:c r="H33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I33" s="189">
+      <s:c r="I33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J33" s="189">
+      <s:c r="J33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K33" s="189">
+      <s:c r="K33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L33" s="189">
+      <s:c r="L33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M33" s="189">
+      <s:c r="M33" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -7174,49 +7373,49 @@
           <s:t>业主年度总支出</s:t>
         </s:is>
       </s:c>
-      <s:c r="C34" s="191">
+      <s:c r="C34" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D34" s="191">
+      <s:c r="D34" s="195">
         <s:f>D31+D32+D33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="E34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="E34" s="195">
         <s:f>E31+E32+E33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="F34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="F34" s="195">
         <s:f>F31+F32+F33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="G34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="G34" s="195">
         <s:f>G31+G32+G33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="H34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="H34" s="195">
         <s:f>H31+H32+H33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="I34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="I34" s="195">
         <s:f>I31+I32+I33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="J34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="J34" s="195">
         <s:f>J31+J32+J33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="K34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="K34" s="195">
         <s:f>K31+K32+K33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="L34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="L34" s="195">
         <s:f>L31+L32+L33</s:f>
-        <s:v>2663056.0</s:v>
-      </s:c>
-      <s:c r="M34" s="191">
+        <s:v>2665000.0</s:v>
+      </s:c>
+      <s:c r="M34" s="195">
         <s:f>M31+M32+M33</s:f>
-        <s:v>2663056.0</s:v>
+        <s:v>2665000.0</s:v>
       </s:c>
     </s:row>
     <s:row r="35">
@@ -7230,49 +7429,49 @@
           <s:t>业主年度净节省</s:t>
         </s:is>
       </s:c>
-      <s:c r="C35" s="191">
+      <s:c r="C35" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D35" s="191">
+      <s:c r="D35" s="195">
         <s:f>D8-D34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="E35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="E35" s="195">
         <s:f>E8-E34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="F35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="F35" s="195">
         <s:f>F8-F34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="G35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="G35" s="195">
         <s:f>G8-G34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="H35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="H35" s="195">
         <s:f>H8-H34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="I35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="I35" s="195">
         <s:f>I8-I34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="J35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="J35" s="195">
         <s:f>J8-J34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="K35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="K35" s="195">
         <s:f>K8-K34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="L35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="L35" s="195">
         <s:f>L8-L34</s:f>
-        <s:v>2944.0</s:v>
-      </s:c>
-      <s:c r="M35" s="191">
+        <s:v>1000.0</s:v>
+      </s:c>
+      <s:c r="M35" s="195">
         <s:f>M8-M34</s:f>
-        <s:v>2944.0</s:v>
+        <s:v>1000.0</s:v>
       </s:c>
     </s:row>
     <s:row r="36">
@@ -7286,47 +7485,47 @@
           <s:t>业主节省率</s:t>
         </s:is>
       </s:c>
-      <s:c r="C36" s="194">
+      <s:c r="C36" s="198">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D36" s="194">
+      <s:c r="D36" s="198">
         <s:f>IF(D8=0,0,D35/D8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E36" s="194">
+      <s:c r="E36" s="198">
         <s:f>IF(E8=0,0,E35/E8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F36" s="194">
+      <s:c r="F36" s="198">
         <s:f>IF(F8=0,0,F35/F8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G36" s="194">
+      <s:c r="G36" s="198">
         <s:f>IF(G8=0,0,G35/G8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H36" s="194">
+      <s:c r="H36" s="198">
         <s:f>IF(H8=0,0,H35/H8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I36" s="194">
+      <s:c r="I36" s="198">
         <s:f>IF(I8=0,0,I35/I8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J36" s="194">
+      <s:c r="J36" s="198">
         <s:f>IF(J8=0,0,J35/J8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K36" s="194">
+      <s:c r="K36" s="198">
         <s:f>IF(K8=0,0,K35/K8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L36" s="194">
+      <s:c r="L36" s="198">
         <s:f>IF(L8=0,0,L35/L8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M36" s="194">
+      <s:c r="M36" s="198">
         <s:f>IF(M8=0,0,M35/M8)</s:f>
         <s:v/>
       </s:c>
@@ -7334,17 +7533,17 @@
     <s:row r="37">
       <s:c r="A37" s="45" t="str"/>
       <s:c r="B37" s="45" t="str"/>
-      <s:c r="C37" s="189" t="n"/>
-      <s:c r="D37" s="189" t="n"/>
-      <s:c r="E37" s="189" t="n"/>
-      <s:c r="F37" s="189" t="n"/>
-      <s:c r="G37" s="189" t="n"/>
-      <s:c r="H37" s="189" t="n"/>
-      <s:c r="I37" s="189" t="n"/>
-      <s:c r="J37" s="189" t="n"/>
-      <s:c r="K37" s="189" t="n"/>
-      <s:c r="L37" s="189" t="n"/>
-      <s:c r="M37" s="189" t="n"/>
+      <s:c r="C37" s="193" t="n"/>
+      <s:c r="D37" s="193" t="n"/>
+      <s:c r="E37" s="193" t="n"/>
+      <s:c r="F37" s="193" t="n"/>
+      <s:c r="G37" s="193" t="n"/>
+      <s:c r="H37" s="193" t="n"/>
+      <s:c r="I37" s="193" t="n"/>
+      <s:c r="J37" s="193" t="n"/>
+      <s:c r="K37" s="193" t="n"/>
+      <s:c r="L37" s="193" t="n"/>
+      <s:c r="M37" s="193" t="n"/>
     </s:row>
     <s:row r="38">
       <s:c r="A38" s="50" t="inlineStr">
@@ -7353,17 +7552,17 @@
         </s:is>
       </s:c>
       <s:c r="B38" s="50" t="str"/>
-      <s:c r="C38" s="190" t="n"/>
-      <s:c r="D38" s="190" t="n"/>
-      <s:c r="E38" s="190" t="n"/>
-      <s:c r="F38" s="190" t="n"/>
-      <s:c r="G38" s="190" t="n"/>
-      <s:c r="H38" s="190" t="n"/>
-      <s:c r="I38" s="190" t="n"/>
-      <s:c r="J38" s="190" t="n"/>
-      <s:c r="K38" s="190" t="n"/>
-      <s:c r="L38" s="190" t="n"/>
-      <s:c r="M38" s="190" t="n"/>
+      <s:c r="C38" s="194" t="n"/>
+      <s:c r="D38" s="194" t="n"/>
+      <s:c r="E38" s="194" t="n"/>
+      <s:c r="F38" s="194" t="n"/>
+      <s:c r="G38" s="194" t="n"/>
+      <s:c r="H38" s="194" t="n"/>
+      <s:c r="I38" s="194" t="n"/>
+      <s:c r="J38" s="194" t="n"/>
+      <s:c r="K38" s="194" t="n"/>
+      <s:c r="L38" s="194" t="n"/>
+      <s:c r="M38" s="194" t="n"/>
     </s:row>
     <s:row r="39">
       <s:c r="A39" s="45" t="inlineStr">
@@ -7432,47 +7631,47 @@
           <s:t>订阅收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C40" s="189">
+      <s:c r="C40" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D40" s="189">
+      <s:c r="D40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(1-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="E40" s="189">
+      <s:c r="E40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(2-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="F40" s="189">
+      <s:c r="F40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(3-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="G40" s="189">
+      <s:c r="G40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(4-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="H40" s="189">
+      <s:c r="H40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(5-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="I40" s="189">
+      <s:c r="I40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(6-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="J40" s="189">
+      <s:c r="J40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(7-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(7-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="K40" s="189">
+      <s:c r="K40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(8-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(8-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="L40" s="189">
+      <s:c r="L40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(9-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(9-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="M40" s="189">
+      <s:c r="M40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(10-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(10-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
@@ -7488,47 +7687,47 @@
           <s:t>其他/第三方收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C41" s="189">
+      <s:c r="C41" s="193">
         <s:f>'02_Inputs'!$D$45</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D41" s="189">
+      <s:c r="D41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E41" s="189">
+      <s:c r="E41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F41" s="189">
+      <s:c r="F41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G41" s="189">
+      <s:c r="G41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H41" s="189">
+      <s:c r="H41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I41" s="189">
+      <s:c r="I41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J41" s="189">
+      <s:c r="J41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K41" s="189">
+      <s:c r="K41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L41" s="189">
+      <s:c r="L41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M41" s="189">
+      <s:c r="M41" s="193">
         <s:f>'04_Mode_Params'!$D$7*(1+'02_Inputs'!$D$16)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -7544,47 +7743,47 @@
           <s:t>资产转让收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C42" s="189">
+      <s:c r="C42" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D42" s="189">
+      <s:c r="D42" s="193">
         <s:f>IF(AND(1='02_Inputs'!$D$36,1&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E42" s="189">
+      <s:c r="E42" s="193">
         <s:f>IF(AND(2='02_Inputs'!$D$36,2&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F42" s="189">
+      <s:c r="F42" s="193">
         <s:f>IF(AND(3='02_Inputs'!$D$36,3&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G42" s="189">
+      <s:c r="G42" s="193">
         <s:f>IF(AND(4='02_Inputs'!$D$36,4&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H42" s="189">
+      <s:c r="H42" s="193">
         <s:f>IF(AND(5='02_Inputs'!$D$36,5&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I42" s="189">
+      <s:c r="I42" s="193">
         <s:f>IF(AND(6='02_Inputs'!$D$36,6&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J42" s="189">
+      <s:c r="J42" s="193">
         <s:f>IF(AND(7='02_Inputs'!$D$36,7&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K42" s="189">
+      <s:c r="K42" s="193">
         <s:f>IF(AND(8='02_Inputs'!$D$36,8&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L42" s="189">
+      <s:c r="L42" s="193">
         <s:f>IF(AND(9='02_Inputs'!$D$36,9&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M42" s="189">
+      <s:c r="M42" s="193">
         <s:f>IF(AND(10='02_Inputs'!$D$36,10&gt;0),'02_Inputs'!$D$37,0)</s:f>
         <s:v/>
       </s:c>
@@ -7600,47 +7799,47 @@
           <s:t>节电后电费总额</s:t>
         </s:is>
       </s:c>
-      <s:c r="C43" s="189">
+      <s:c r="C43" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D43" s="189">
+      <s:c r="D43" s="193">
         <s:f>D6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E43" s="189">
+      <s:c r="E43" s="193">
         <s:f>E6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F43" s="189">
+      <s:c r="F43" s="193">
         <s:f>F6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G43" s="189">
+      <s:c r="G43" s="193">
         <s:f>G6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H43" s="189">
+      <s:c r="H43" s="193">
         <s:f>H6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I43" s="189">
+      <s:c r="I43" s="193">
         <s:f>I6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J43" s="189">
+      <s:c r="J43" s="193">
         <s:f>J6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K43" s="189">
+      <s:c r="K43" s="193">
         <s:f>K6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L43" s="189">
+      <s:c r="L43" s="193">
         <s:f>L6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M43" s="189">
+      <s:c r="M43" s="193">
         <s:f>M6*(1-'04_Mode_Params'!$D$8)</s:f>
         <s:v/>
       </s:c>
@@ -7880,47 +8079,47 @@
           <s:t>年度总收入</s:t>
         </s:is>
       </s:c>
-      <s:c r="C48" s="191">
+      <s:c r="C48" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D48" s="191">
+      <s:c r="D48" s="195">
         <s:f>D40+D41+D42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E48" s="191">
+      <s:c r="E48" s="195">
         <s:f>E40+E41+E42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F48" s="191">
+      <s:c r="F48" s="195">
         <s:f>F40+F41+F42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G48" s="191">
+      <s:c r="G48" s="195">
         <s:f>G40+G41+G42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H48" s="191">
+      <s:c r="H48" s="195">
         <s:f>H40+H41+H42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I48" s="191">
+      <s:c r="I48" s="195">
         <s:f>I40+I41+I42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J48" s="191">
+      <s:c r="J48" s="195">
         <s:f>J40+J41+J42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K48" s="191">
+      <s:c r="K48" s="195">
         <s:f>K40+K41+K42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L48" s="191">
+      <s:c r="L48" s="195">
         <s:f>L40+L41+L42</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M48" s="191">
+      <s:c r="M48" s="195">
         <s:f>M40+M41+M42</s:f>
         <s:v/>
       </s:c>
@@ -7936,47 +8135,47 @@
           <s:t>年度总现金成本</s:t>
         </s:is>
       </s:c>
-      <s:c r="C49" s="191">
+      <s:c r="C49" s="195">
         <s:f>C39</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D49" s="191">
+      <s:c r="D49" s="195">
         <s:f>D39+D44+D45+D46+D47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E49" s="191">
+      <s:c r="E49" s="195">
         <s:f>E39+E44+E45+E46+E47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F49" s="191">
+      <s:c r="F49" s="195">
         <s:f>F39+F44+F45+F46+F47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G49" s="191">
+      <s:c r="G49" s="195">
         <s:f>G39+G44+G45+G46+G47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H49" s="191">
+      <s:c r="H49" s="195">
         <s:f>H39+H44+H45+H46+H47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I49" s="191">
+      <s:c r="I49" s="195">
         <s:f>I39+I44+I45+I46+I47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J49" s="191">
+      <s:c r="J49" s="195">
         <s:f>J39+J44+J45+J46+J47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K49" s="191">
+      <s:c r="K49" s="195">
         <s:f>K39+K44+K45+K46+K47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L49" s="191">
+      <s:c r="L49" s="195">
         <s:f>L39+L44+L45+L46+L47</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M49" s="191">
+      <s:c r="M49" s="195">
         <s:f>M39+M44+M45+M46+M47</s:f>
         <s:v/>
       </s:c>
@@ -7992,47 +8191,47 @@
           <s:t>年度净现金流</s:t>
         </s:is>
       </s:c>
-      <s:c r="C50" s="191">
+      <s:c r="C50" s="195">
         <s:f>C48-C49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D50" s="191">
+      <s:c r="D50" s="195">
         <s:f>D48-D49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E50" s="191">
+      <s:c r="E50" s="195">
         <s:f>E48-E49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F50" s="191">
+      <s:c r="F50" s="195">
         <s:f>F48-F49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G50" s="191">
+      <s:c r="G50" s="195">
         <s:f>G48-G49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H50" s="191">
+      <s:c r="H50" s="195">
         <s:f>H48-H49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I50" s="191">
+      <s:c r="I50" s="195">
         <s:f>I48-I49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J50" s="191">
+      <s:c r="J50" s="195">
         <s:f>J48-J49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K50" s="191">
+      <s:c r="K50" s="195">
         <s:f>K48-K49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L50" s="191">
+      <s:c r="L50" s="195">
         <s:f>L48-L49</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M50" s="191">
+      <s:c r="M50" s="195">
         <s:f>M48-M49</s:f>
         <s:v/>
       </s:c>
@@ -8048,47 +8247,47 @@
           <s:t>累计现金流</s:t>
         </s:is>
       </s:c>
-      <s:c r="C51" s="191">
+      <s:c r="C51" s="195">
         <s:f>C50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D51" s="191">
+      <s:c r="D51" s="195">
         <s:f>C51+D50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E51" s="191">
+      <s:c r="E51" s="195">
         <s:f>D51+E50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F51" s="191">
+      <s:c r="F51" s="195">
         <s:f>E51+F50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G51" s="191">
+      <s:c r="G51" s="195">
         <s:f>F51+G50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H51" s="191">
+      <s:c r="H51" s="195">
         <s:f>G51+H50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I51" s="191">
+      <s:c r="I51" s="195">
         <s:f>H51+I50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J51" s="191">
+      <s:c r="J51" s="195">
         <s:f>I51+J50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K51" s="191">
+      <s:c r="K51" s="195">
         <s:f>J51+K50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L51" s="191">
+      <s:c r="L51" s="195">
         <s:f>K51+L50</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M51" s="191">
+      <s:c r="M51" s="195">
         <s:f>L51+M50</s:f>
         <s:v>16503599.999999998</s:v>
       </s:c>
@@ -8104,20 +8303,20 @@
           <s:t>NPV</s:t>
         </s:is>
       </s:c>
-      <s:c r="C52" s="192">
+      <s:c r="C52" s="196">
         <s:f>NPV('02_Inputs'!$D$13,D50:M50)+C50</s:f>
         <s:v>8585493.51572983</s:v>
       </s:c>
-      <s:c r="D52" s="189" t="n"/>
-      <s:c r="E52" s="189" t="n"/>
-      <s:c r="F52" s="189" t="n"/>
-      <s:c r="G52" s="189" t="n"/>
-      <s:c r="H52" s="189" t="n"/>
-      <s:c r="I52" s="189" t="n"/>
-      <s:c r="J52" s="189" t="n"/>
-      <s:c r="K52" s="189" t="n"/>
-      <s:c r="L52" s="189" t="n"/>
-      <s:c r="M52" s="189" t="n"/>
+      <s:c r="D52" s="193" t="n"/>
+      <s:c r="E52" s="193" t="n"/>
+      <s:c r="F52" s="193" t="n"/>
+      <s:c r="G52" s="193" t="n"/>
+      <s:c r="H52" s="193" t="n"/>
+      <s:c r="I52" s="193" t="n"/>
+      <s:c r="J52" s="193" t="n"/>
+      <s:c r="K52" s="193" t="n"/>
+      <s:c r="L52" s="193" t="n"/>
+      <s:c r="M52" s="193" t="n"/>
     </s:row>
     <s:row r="53">
       <s:c r="A53" s="45" t="inlineStr">
@@ -8130,20 +8329,20 @@
           <s:t>IRR</s:t>
         </s:is>
       </s:c>
-      <s:c r="C53" s="193">
+      <s:c r="C53" s="197">
         <s:f>IFERROR(IRR(C50:M50),"n/a")</s:f>
         <s:v>0.779970162677768</s:v>
       </s:c>
-      <s:c r="D53" s="194" t="n"/>
-      <s:c r="E53" s="194" t="n"/>
-      <s:c r="F53" s="194" t="n"/>
-      <s:c r="G53" s="194" t="n"/>
-      <s:c r="H53" s="194" t="n"/>
-      <s:c r="I53" s="194" t="n"/>
-      <s:c r="J53" s="194" t="n"/>
-      <s:c r="K53" s="194" t="n"/>
-      <s:c r="L53" s="194" t="n"/>
-      <s:c r="M53" s="194" t="n"/>
+      <s:c r="D53" s="198" t="n"/>
+      <s:c r="E53" s="198" t="n"/>
+      <s:c r="F53" s="198" t="n"/>
+      <s:c r="G53" s="198" t="n"/>
+      <s:c r="H53" s="198" t="n"/>
+      <s:c r="I53" s="198" t="n"/>
+      <s:c r="J53" s="198" t="n"/>
+      <s:c r="K53" s="198" t="n"/>
+      <s:c r="L53" s="198" t="n"/>
+      <s:c r="M53" s="198" t="n"/>
     </s:row>
     <s:row r="54">
       <s:c r="A54" s="45" t="inlineStr">
@@ -8156,20 +8355,20 @@
           <s:t>10年ROI</s:t>
         </s:is>
       </s:c>
-      <s:c r="C54" s="195">
+      <s:c r="C54" s="199">
         <s:f>IF(C39=0,"n/a",SUM(C50:M50)/C39)</s:f>
         <s:v>5.945357970277448</s:v>
       </s:c>
-      <s:c r="D54" s="194" t="n"/>
-      <s:c r="E54" s="194" t="n"/>
-      <s:c r="F54" s="194" t="n"/>
-      <s:c r="G54" s="194" t="n"/>
-      <s:c r="H54" s="194" t="n"/>
-      <s:c r="I54" s="194" t="n"/>
-      <s:c r="J54" s="194" t="n"/>
-      <s:c r="K54" s="194" t="n"/>
-      <s:c r="L54" s="194" t="n"/>
-      <s:c r="M54" s="194" t="n"/>
+      <s:c r="D54" s="198" t="n"/>
+      <s:c r="E54" s="198" t="n"/>
+      <s:c r="F54" s="198" t="n"/>
+      <s:c r="G54" s="198" t="n"/>
+      <s:c r="H54" s="198" t="n"/>
+      <s:c r="I54" s="198" t="n"/>
+      <s:c r="J54" s="198" t="n"/>
+      <s:c r="K54" s="198" t="n"/>
+      <s:c r="L54" s="198" t="n"/>
+      <s:c r="M54" s="198" t="n"/>
     </s:row>
     <s:row r="55">
       <s:c r="A55" s="45" t="inlineStr">
@@ -8182,35 +8381,35 @@
           <s:t>静态回收期</s:t>
         </s:is>
       </s:c>
-      <s:c r="C55" s="196">
+      <s:c r="C55" s="200">
         <s:f>IF(M51&lt;0,"未回收",IF(C51&gt;=0,C$4,IF(D51&gt;=0,D$4,IF(E51&gt;=0,E$4,IF(F51&gt;=0,F$4,IF(G51&gt;=0,G$4,IF(H51&gt;=0,H$4,IF(I51&gt;=0,I$4,IF(J51&gt;=0,J$4,IF(K51&gt;=0,K$4,IF(L51&gt;=0,L$4,M$4)))))))))))</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D55" s="197" t="n"/>
-      <s:c r="E55" s="197" t="n"/>
-      <s:c r="F55" s="197" t="n"/>
-      <s:c r="G55" s="197" t="n"/>
-      <s:c r="H55" s="197" t="n"/>
-      <s:c r="I55" s="197" t="n"/>
-      <s:c r="J55" s="197" t="n"/>
-      <s:c r="K55" s="197" t="n"/>
-      <s:c r="L55" s="197" t="n"/>
-      <s:c r="M55" s="197" t="n"/>
+      <s:c r="D55" s="201" t="n"/>
+      <s:c r="E55" s="201" t="n"/>
+      <s:c r="F55" s="201" t="n"/>
+      <s:c r="G55" s="201" t="n"/>
+      <s:c r="H55" s="201" t="n"/>
+      <s:c r="I55" s="201" t="n"/>
+      <s:c r="J55" s="201" t="n"/>
+      <s:c r="K55" s="201" t="n"/>
+      <s:c r="L55" s="201" t="n"/>
+      <s:c r="M55" s="201" t="n"/>
     </s:row>
     <s:row r="56">
       <s:c r="A56" s="45" t="str"/>
       <s:c r="B56" s="45" t="str"/>
-      <s:c r="C56" s="189" t="n"/>
-      <s:c r="D56" s="189" t="n"/>
-      <s:c r="E56" s="189" t="n"/>
-      <s:c r="F56" s="189" t="n"/>
-      <s:c r="G56" s="189" t="n"/>
-      <s:c r="H56" s="189" t="n"/>
-      <s:c r="I56" s="189" t="n"/>
-      <s:c r="J56" s="189" t="n"/>
-      <s:c r="K56" s="189" t="n"/>
-      <s:c r="L56" s="189" t="n"/>
-      <s:c r="M56" s="189" t="n"/>
+      <s:c r="C56" s="193" t="n"/>
+      <s:c r="D56" s="193" t="n"/>
+      <s:c r="E56" s="193" t="n"/>
+      <s:c r="F56" s="193" t="n"/>
+      <s:c r="G56" s="193" t="n"/>
+      <s:c r="H56" s="193" t="n"/>
+      <s:c r="I56" s="193" t="n"/>
+      <s:c r="J56" s="193" t="n"/>
+      <s:c r="K56" s="193" t="n"/>
+      <s:c r="L56" s="193" t="n"/>
+      <s:c r="M56" s="193" t="n"/>
     </s:row>
     <s:row r="57">
       <s:c r="A57" s="50" t="inlineStr">
@@ -8219,17 +8418,17 @@
         </s:is>
       </s:c>
       <s:c r="B57" s="50" t="str"/>
-      <s:c r="C57" s="190" t="n"/>
-      <s:c r="D57" s="190" t="n"/>
-      <s:c r="E57" s="190" t="n"/>
-      <s:c r="F57" s="190" t="n"/>
-      <s:c r="G57" s="190" t="n"/>
-      <s:c r="H57" s="190" t="n"/>
-      <s:c r="I57" s="190" t="n"/>
-      <s:c r="J57" s="190" t="n"/>
-      <s:c r="K57" s="190" t="n"/>
-      <s:c r="L57" s="190" t="n"/>
-      <s:c r="M57" s="190" t="n"/>
+      <s:c r="C57" s="194" t="n"/>
+      <s:c r="D57" s="194" t="n"/>
+      <s:c r="E57" s="194" t="n"/>
+      <s:c r="F57" s="194" t="n"/>
+      <s:c r="G57" s="194" t="n"/>
+      <s:c r="H57" s="194" t="n"/>
+      <s:c r="I57" s="194" t="n"/>
+      <s:c r="J57" s="194" t="n"/>
+      <s:c r="K57" s="194" t="n"/>
+      <s:c r="L57" s="194" t="n"/>
+      <s:c r="M57" s="194" t="n"/>
     </s:row>
     <s:row r="58">
       <s:c r="A58" s="45" t="inlineStr">
@@ -8242,47 +8441,47 @@
           <s:t>业主支付电费</s:t>
         </s:is>
       </s:c>
-      <s:c r="C58" s="189">
+      <s:c r="C58" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D58" s="189">
+      <s:c r="D58" s="193">
         <s:f>D43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="E58" s="189">
+      <s:c r="E58" s="193">
         <s:f>E43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="F58" s="189">
+      <s:c r="F58" s="193">
         <s:f>F43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="G58" s="189">
+      <s:c r="G58" s="193">
         <s:f>G43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="H58" s="189">
+      <s:c r="H58" s="193">
         <s:f>H43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="I58" s="189">
+      <s:c r="I58" s="193">
         <s:f>I43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="J58" s="189">
+      <s:c r="J58" s="193">
         <s:f>J43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="K58" s="189">
+      <s:c r="K58" s="193">
         <s:f>K43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="L58" s="189">
+      <s:c r="L58" s="193">
         <s:f>L43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
-      <s:c r="M58" s="189">
+      <s:c r="M58" s="193">
         <s:f>M43*(1-'04_Mode_Params'!$D$10)</s:f>
         <s:v>308400.00000000006</s:v>
       </s:c>
@@ -8298,47 +8497,47 @@
           <s:t>订阅费支出</s:t>
         </s:is>
       </s:c>
-      <s:c r="C59" s="189">
+      <s:c r="C59" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D59" s="189">
+      <s:c r="D59" s="193">
         <s:f>D40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="E59" s="189">
+      <s:c r="E59" s="193">
         <s:f>E40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="F59" s="189">
+      <s:c r="F59" s="193">
         <s:f>F40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="G59" s="189">
+      <s:c r="G59" s="193">
         <s:f>G40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="H59" s="189">
+      <s:c r="H59" s="193">
         <s:f>H40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="I59" s="189">
+      <s:c r="I59" s="193">
         <s:f>I40</s:f>
         <s:v>2350000.0</s:v>
       </s:c>
-      <s:c r="J59" s="189">
+      <s:c r="J59" s="193">
         <s:f>J40</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="K59" s="189">
+      <s:c r="K59" s="193">
         <s:f>K40</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="L59" s="189">
+      <s:c r="L59" s="193">
         <s:f>L40</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
-      <s:c r="M59" s="189">
+      <s:c r="M59" s="193">
         <s:f>M40</s:f>
         <s:v>2100000.0</s:v>
       </s:c>
@@ -8354,47 +8553,47 @@
           <s:t>业主保留管理成本</s:t>
         </s:is>
       </s:c>
-      <s:c r="C60" s="189">
+      <s:c r="C60" s="193">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D60" s="189">
+      <s:c r="D60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(1-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E60" s="189">
+      <s:c r="E60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(2-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F60" s="189">
+      <s:c r="F60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(3-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G60" s="189">
+      <s:c r="G60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(4-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H60" s="189">
+      <s:c r="H60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(5-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I60" s="189">
+      <s:c r="I60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(6-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J60" s="189">
+      <s:c r="J60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(7-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K60" s="189">
+      <s:c r="K60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(8-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L60" s="189">
+      <s:c r="L60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(9-1)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M60" s="189">
+      <s:c r="M60" s="193">
         <s:f>'02_Inputs'!$D$17*(1+'02_Inputs'!$D$15)^(10-1)</s:f>
         <s:v/>
       </s:c>
@@ -8410,47 +8609,47 @@
           <s:t>业主年度总支出</s:t>
         </s:is>
       </s:c>
-      <s:c r="C61" s="191">
+      <s:c r="C61" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D61" s="191">
+      <s:c r="D61" s="195">
         <s:f>D58+D59+D60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="E61" s="191">
+      <s:c r="E61" s="195">
         <s:f>E58+E59+E60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="F61" s="191">
+      <s:c r="F61" s="195">
         <s:f>F58+F59+F60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="G61" s="191">
+      <s:c r="G61" s="195">
         <s:f>G58+G59+G60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="H61" s="191">
+      <s:c r="H61" s="195">
         <s:f>H58+H59+H60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="I61" s="191">
+      <s:c r="I61" s="195">
         <s:f>I58+I59+I60</s:f>
         <s:v>2658400.0</s:v>
       </s:c>
-      <s:c r="J61" s="191">
+      <s:c r="J61" s="195">
         <s:f>J58+J59+J60</s:f>
         <s:v>2408400.0</s:v>
       </s:c>
-      <s:c r="K61" s="191">
+      <s:c r="K61" s="195">
         <s:f>K58+K59+K60</s:f>
         <s:v>2408400.0</s:v>
       </s:c>
-      <s:c r="L61" s="191">
+      <s:c r="L61" s="195">
         <s:f>L58+L59+L60</s:f>
         <s:v>2408400.0</s:v>
       </s:c>
-      <s:c r="M61" s="191">
+      <s:c r="M61" s="195">
         <s:f>M58+M59+M60</s:f>
         <s:v>2408400.0</s:v>
       </s:c>
@@ -8466,47 +8665,47 @@
           <s:t>业主年度净节省</s:t>
         </s:is>
       </s:c>
-      <s:c r="C62" s="191">
+      <s:c r="C62" s="195">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D62" s="191">
+      <s:c r="D62" s="195">
         <s:f>D8-D61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="E62" s="191">
+      <s:c r="E62" s="195">
         <s:f>E8-E61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="F62" s="191">
+      <s:c r="F62" s="195">
         <s:f>F8-F61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="G62" s="191">
+      <s:c r="G62" s="195">
         <s:f>G8-G61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="H62" s="191">
+      <s:c r="H62" s="195">
         <s:f>H8-H61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="I62" s="191">
+      <s:c r="I62" s="195">
         <s:f>I8-I61</s:f>
         <s:v>7600.0</s:v>
       </s:c>
-      <s:c r="J62" s="191">
+      <s:c r="J62" s="195">
         <s:f>J8-J61</s:f>
         <s:v>257600.0</s:v>
       </s:c>
-      <s:c r="K62" s="191">
+      <s:c r="K62" s="195">
         <s:f>K8-K61</s:f>
         <s:v>257600.0</s:v>
       </s:c>
-      <s:c r="L62" s="191">
+      <s:c r="L62" s="195">
         <s:f>L8-L61</s:f>
         <s:v>257600.0</s:v>
       </s:c>
-      <s:c r="M62" s="191">
+      <s:c r="M62" s="195">
         <s:f>M8-M61</s:f>
         <s:v>257600.0</s:v>
       </s:c>
@@ -8522,47 +8721,47 @@
           <s:t>业主节省率</s:t>
         </s:is>
       </s:c>
-      <s:c r="C63" s="194">
+      <s:c r="C63" s="198">
         <s:f>0</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D63" s="194">
+      <s:c r="D63" s="198">
         <s:f>IF(D8=0,0,D62/D8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E63" s="194">
+      <s:c r="E63" s="198">
         <s:f>IF(E8=0,0,E62/E8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F63" s="194">
+      <s:c r="F63" s="198">
         <s:f>IF(F8=0,0,F62/F8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G63" s="194">
+      <s:c r="G63" s="198">
         <s:f>IF(G8=0,0,G62/G8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H63" s="194">
+      <s:c r="H63" s="198">
         <s:f>IF(H8=0,0,H62/H8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="I63" s="194">
+      <s:c r="I63" s="198">
         <s:f>IF(I8=0,0,I62/I8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="J63" s="194">
+      <s:c r="J63" s="198">
         <s:f>IF(J8=0,0,J62/J8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="K63" s="194">
+      <s:c r="K63" s="198">
         <s:f>IF(K8=0,0,K62/K8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="L63" s="194">
+      <s:c r="L63" s="198">
         <s:f>IF(L8=0,0,L62/L8)</s:f>
         <s:v/>
       </s:c>
-      <s:c r="M63" s="194">
+      <s:c r="M63" s="198">
         <s:f>IF(M8=0,0,M62/M8)</s:f>
         <s:v/>
       </s:c>
@@ -8681,19 +8880,19 @@
           <s:t>能源托管/EMC</s:t>
         </s:is>
       </s:c>
-      <s:c r="B5" s="189">
+      <s:c r="B5" s="193">
         <s:f>('04_Mode_Params'!C5+'02_Inputs'!$D$5*('04_Mode_Params'!C17-'04_Mode_Params'!C7))/'02_Inputs'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C5" s="189">
+      <s:c r="C5" s="193">
         <s:f>'04_Mode_Params'!C5/(IF('02_Inputs'!$D$13=0,'02_Inputs'!$D$5,(1-(1+'02_Inputs'!$D$13)^-'02_Inputs'!$D$5)/'02_Inputs'!$D$13))+'04_Mode_Params'!C17-'04_Mode_Params'!C7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D5" s="189">
+      <s:c r="D5" s="193">
         <s:f>'04_Mode_Params'!C6</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E5" s="189">
+      <s:c r="E5" s="193">
         <s:f>D5-C5</s:f>
         <s:v/>
       </s:c>
@@ -8709,19 +8908,19 @@
           <s:t>LaaS/AI订阅</s:t>
         </s:is>
       </s:c>
-      <s:c r="B6" s="189">
+      <s:c r="B6" s="193">
         <s:f>('04_Mode_Params'!D5+'02_Inputs'!$D$5*('04_Mode_Params'!D17-'04_Mode_Params'!D7))/'02_Inputs'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C6" s="189">
+      <s:c r="C6" s="193">
         <s:f>'04_Mode_Params'!D5/(IF('02_Inputs'!$D$13=0,'02_Inputs'!$D$5,(1-(1+'02_Inputs'!$D$13)^-'02_Inputs'!$D$5)/'02_Inputs'!$D$13))+'04_Mode_Params'!D17-'04_Mode_Params'!D7</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D6" s="189">
+      <s:c r="D6" s="193">
         <s:f>'04_Mode_Params'!D6</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E6" s="189">
+      <s:c r="E6" s="193">
         <s:f>D6-C6</s:f>
         <s:v/>
       </s:c>
@@ -8779,31 +8978,31 @@
           <s:t>能源托管/EMC 10年ROI</s:t>
         </s:is>
       </s:c>
-      <s:c r="B10" s="198">
+      <s:c r="B10" s="202">
         <s:f>((800000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C10" s="198">
+      <s:c r="C10" s="202">
         <s:f>((900000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D10" s="198">
+      <s:c r="D10" s="202">
         <s:f>((1000000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E10" s="198">
+      <s:c r="E10" s="202">
         <s:f>((1100000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F10" s="198">
+      <s:c r="F10" s="202">
         <s:f>((1200000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G10" s="198">
+      <s:c r="G10" s="202">
         <s:f>((1400000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H10" s="198">
+      <s:c r="H10" s="202">
         <s:f>((1600000+'04_Mode_Params'!$C$7-'04_Mode_Params'!$C$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$C$5)/'04_Mode_Params'!$C$5</s:f>
         <s:v/>
       </s:c>
@@ -8849,31 +9048,31 @@
           <s:t>LaaS/AI订阅 10年ROI</s:t>
         </s:is>
       </s:c>
-      <s:c r="B12" s="198">
+      <s:c r="B12" s="202">
         <s:f>((800000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C12" s="198">
+      <s:c r="C12" s="202">
         <s:f>((900000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D12" s="198">
+      <s:c r="D12" s="202">
         <s:f>((1000000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E12" s="198">
+      <s:c r="E12" s="202">
         <s:f>((1100000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F12" s="198">
+      <s:c r="F12" s="202">
         <s:f>((1200000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G12" s="198">
+      <s:c r="G12" s="202">
         <s:f>((1400000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H12" s="198">
+      <s:c r="H12" s="202">
         <s:f>((1600000+'04_Mode_Params'!$D$7-'04_Mode_Params'!$D$17)*'02_Inputs'!$D$5-'04_Mode_Params'!$D$5)/'04_Mode_Params'!$D$5</s:f>
         <s:v/>
       </s:c>
@@ -8996,31 +9195,31 @@
           <s:t>能源托管/EMC 业主节省率</s:t>
         </s:is>
       </s:c>
-      <s:c r="B18" s="198">
+      <s:c r="B18" s="202">
         <s:f>B17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C18" s="198">
+      <s:c r="C18" s="202">
         <s:f>C17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D18" s="198">
+      <s:c r="D18" s="202">
         <s:f>D17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E18" s="198">
+      <s:c r="E18" s="202">
         <s:f>E17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F18" s="198">
+      <s:c r="F18" s="202">
         <s:f>F17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G18" s="198">
+      <s:c r="G18" s="202">
         <s:f>G17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H18" s="198">
+      <s:c r="H18" s="202">
         <s:f>H17/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
@@ -9066,31 +9265,31 @@
           <s:t>LaaS/AI订阅 业主节省率</s:t>
         </s:is>
       </s:c>
-      <s:c r="B20" s="198">
+      <s:c r="B20" s="202">
         <s:f>B19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="C20" s="198">
+      <s:c r="C20" s="202">
         <s:f>C19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="D20" s="198">
+      <s:c r="D20" s="202">
         <s:f>D19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="E20" s="198">
+      <s:c r="E20" s="202">
         <s:f>E19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="F20" s="198">
+      <s:c r="F20" s="202">
         <s:f>F19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="G20" s="198">
+      <s:c r="G20" s="202">
         <s:f>G19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>
-      <s:c r="H20" s="198">
+      <s:c r="H20" s="202">
         <s:f>H19/'03_Baseline'!$D$15</s:f>
         <s:v/>
       </s:c>

--- a/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
+++ b/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
@@ -1055,7 +1055,7 @@
       </s:c>
       <s:c r="C6" s="168">
         <s:f>'03_Baseline'!D5</s:f>
-        <s:v/>
+        <s:v>4568.0</s:v>
       </s:c>
       <s:c r="D6" s="130" t="inlineStr">
         <s:is>
@@ -1081,7 +1081,7 @@
       </s:c>
       <s:c r="C7" s="169">
         <s:f>'03_Baseline'!D11</s:f>
-        <s:v/>
+        <s:v>0.6900001496778997</s:v>
       </s:c>
       <s:c r="D7" s="130" t="inlineStr">
         <s:is>
@@ -1107,7 +1107,7 @@
       </s:c>
       <s:c r="C8" s="170">
         <s:f>'03_Baseline'!D12</s:f>
-        <s:v/>
+        <s:v>2120554.0</s:v>
       </s:c>
       <s:c r="D8" s="130" t="inlineStr">
         <s:is>
@@ -1133,7 +1133,7 @@
       </s:c>
       <s:c r="C9" s="170">
         <s:f>'03_Baseline'!D14</s:f>
-        <s:v/>
+        <s:v>609997.0</s:v>
       </s:c>
       <s:c r="D9" s="130" t="inlineStr">
         <s:is>
@@ -1159,7 +1159,7 @@
       </s:c>
       <s:c r="C10" s="170">
         <s:f>'03_Baseline'!D16</s:f>
-        <s:v/>
+        <s:v>2600000.0</s:v>
       </s:c>
       <s:c r="D10" s="130" t="inlineStr">
         <s:is>
@@ -1185,7 +1185,7 @@
       </s:c>
       <s:c r="C11" s="130">
         <s:f>'04_Mode_Params'!C6='04_Mode_Params'!D6</s:f>
-        <s:v/>
+        <s:v>0.0</s:v>
       </s:c>
       <s:c r="D11" s="130" t="inlineStr">
         <s:is>
@@ -1269,7 +1269,7 @@
       </s:c>
       <s:c r="C15" s="171">
         <s:f>'04_Mode_Params'!C8</s:f>
-        <s:v>0.5</s:v>
+        <s:v>0.515219607706288</s:v>
       </s:c>
       <s:c r="D15" s="171">
         <s:f>'04_Mode_Params'!D8</s:f>
@@ -1308,11 +1308,11 @@
       </s:c>
       <s:c r="C16" s="172">
         <s:f>'03_Baseline'!D10*'04_Mode_Params'!C8</s:f>
-        <s:v>2056000.0</s:v>
+        <s:v>1583406.902897073</s:v>
       </s:c>
       <s:c r="D16" s="172">
         <s:f>'03_Baseline'!D10*'04_Mode_Params'!D8</s:f>
-        <s:v>3495200.0</s:v>
+        <s:v>2612276.1</s:v>
       </s:c>
       <s:c r="E16" s="172">
         <s:f>D16-C16</s:f>
@@ -1347,11 +1347,11 @@
       </s:c>
       <s:c r="C17" s="172">
         <s:f>'03_Baseline'!D12-'04_Mode_Params'!C9</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1092551.0</s:v>
       </s:c>
       <s:c r="D17" s="172">
         <s:f>'03_Baseline'!D12-'04_Mode_Params'!D9</s:f>
-        <s:v>1747600.0</s:v>
+        <s:v>1802470.9</s:v>
       </s:c>
       <s:c r="E17" s="172">
         <s:f>D17-C17</s:f>
@@ -1386,15 +1386,15 @@
       </s:c>
       <s:c r="C18" s="173">
         <s:f>'04_Mode_Params'!C19</s:f>
-        <s:v/>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="D18" s="173">
         <s:f>'04_Mode_Params'!D19</s:f>
-        <s:v/>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="E18" s="173">
         <s:f>C18-D18</s:f>
-        <s:v/>
+        <s:v>712219.8999999999</s:v>
       </s:c>
       <s:c r="F18" s="45" t="inlineStr">
         <s:is>
@@ -1425,15 +1425,15 @@
       </s:c>
       <s:c r="C19" s="173">
         <s:f>'04_Mode_Params'!C20</s:f>
-        <s:v/>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="D19" s="173">
         <s:f>'04_Mode_Params'!D20</s:f>
-        <s:v/>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="E19" s="173">
         <s:f>D19-C19</s:f>
-        <s:v/>
+        <s:v>712219.8999999999</s:v>
       </s:c>
       <s:c r="F19" s="45" t="inlineStr">
         <s:is>
@@ -1464,15 +1464,15 @@
       </s:c>
       <s:c r="C20" s="173">
         <s:f>'04_Mode_Params'!C16</s:f>
-        <s:v/>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="D20" s="173">
         <s:f>'04_Mode_Params'!D16</s:f>
-        <s:v/>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="E20" s="173">
         <s:f>D20-C20</s:f>
-        <s:v/>
+        <s:v>-2300.0</s:v>
       </s:c>
       <s:c r="F20" s="45" t="inlineStr">
         <s:is>
@@ -1503,15 +1503,15 @@
       </s:c>
       <s:c r="C21" s="173">
         <s:f>'04_Mode_Params'!C17</s:f>
-        <s:v/>
+        <s:v>609997.0</s:v>
       </s:c>
       <s:c r="D21" s="173">
         <s:f>'04_Mode_Params'!D17</s:f>
-        <s:v/>
+        <s:v>245700.00000000006</s:v>
       </s:c>
       <s:c r="E21" s="173">
         <s:f>C21-D21</s:f>
-        <s:v/>
+        <s:v>364296.99999999994</s:v>
       </s:c>
       <s:c r="F21" s="45" t="inlineStr">
         <s:is>
@@ -1542,15 +1542,15 @@
       </s:c>
       <s:c r="C22" s="173">
         <s:f>'04_Mode_Params'!C13</s:f>
-        <s:v/>
+        <s:v>394236.8839841539</s:v>
       </s:c>
       <s:c r="D22" s="173">
         <s:f>'04_Mode_Params'!D13</s:f>
-        <s:v/>
+        <s:v>86995.47333608932</s:v>
       </s:c>
       <s:c r="E22" s="173">
         <s:f>C22-D22</s:f>
-        <s:v/>
+        <s:v>307241.4106480646</s:v>
       </s:c>
       <s:c r="F22" s="45" t="inlineStr">
         <s:is>
@@ -1581,15 +1581,15 @@
       </s:c>
       <s:c r="C23" s="173">
         <s:f>'04_Mode_Params'!C14+'04_Mode_Params'!C15</s:f>
-        <s:v/>
+        <s:v>161820.08701188455</s:v>
       </s:c>
       <s:c r="D23" s="173">
         <s:f>'04_Mode_Params'!D14+'04_Mode_Params'!D15</s:f>
-        <s:v/>
+        <s:v>111093.16866473753</s:v>
       </s:c>
       <s:c r="E23" s="173">
         <s:f>C23-D23</s:f>
-        <s:v/>
+        <s:v>50726.91834714702</s:v>
       </s:c>
       <s:c r="F23" s="45" t="inlineStr">
         <s:is>
@@ -1620,15 +1620,15 @@
       </s:c>
       <s:c r="C24" s="173">
         <s:f>'04_Mode_Params'!C18</s:f>
-        <s:v/>
+        <s:v>1732303.0</s:v>
       </s:c>
       <s:c r="D24" s="173">
         <s:f>'04_Mode_Params'!D18</s:f>
-        <s:v/>
+        <s:v>2094300.0</s:v>
       </s:c>
       <s:c r="E24" s="173">
         <s:f>D24-C24</s:f>
-        <s:v/>
+        <s:v>361997.0</s:v>
       </s:c>
       <s:c r="F24" s="45" t="inlineStr">
         <s:is>
@@ -1659,15 +1659,15 @@
       </s:c>
       <s:c r="C25" s="173">
         <s:f>'04_Mode_Params'!C5</s:f>
-        <s:v/>
+        <s:v>3539400.0</s:v>
       </s:c>
       <s:c r="D25" s="173">
         <s:f>'04_Mode_Params'!D5</s:f>
-        <s:v/>
+        <s:v>3539400.0</s:v>
       </s:c>
       <s:c r="E25" s="173">
         <s:f>C25-D25</s:f>
-        <s:v/>
+        <s:v>0.0</s:v>
       </s:c>
       <s:c r="F25" s="45" t="inlineStr">
         <s:is>
@@ -1698,15 +1698,15 @@
       </s:c>
       <s:c r="C26" s="173">
         <s:f>'05_Annual_Model'!M24</s:f>
-        <s:v/>
+        <s:v>13783630.0</s:v>
       </s:c>
       <s:c r="D26" s="173">
         <s:f>'05_Annual_Model'!M51</s:f>
-        <s:v/>
+        <s:v>16403599.99999997</s:v>
       </s:c>
       <s:c r="E26" s="173">
         <s:f>D26-C26</s:f>
-        <s:v/>
+        <s:v>2619969.99999997</s:v>
       </s:c>
       <s:c r="F26" s="45" t="inlineStr">
         <s:is>
@@ -1737,15 +1737,15 @@
       </s:c>
       <s:c r="C27" s="173">
         <s:f>'05_Annual_Model'!C25</s:f>
-        <s:v/>
+        <s:v>7423046.099119451</s:v>
       </s:c>
       <s:c r="D27" s="173">
         <s:f>'05_Annual_Model'!C52</s:f>
-        <s:v/>
+        <s:v>8525947.237637723</s:v>
       </s:c>
       <s:c r="E27" s="173">
         <s:f>D27-C27</s:f>
-        <s:v/>
+        <s:v>1102901.138518272</s:v>
       </s:c>
       <s:c r="F27" s="45" t="inlineStr">
         <s:is>
@@ -1776,15 +1776,15 @@
       </s:c>
       <s:c r="C28" s="171">
         <s:f>'05_Annual_Model'!C26</s:f>
-        <s:v/>
+        <s:v>0.4797080973744201</s:v>
       </s:c>
       <s:c r="D28" s="171">
         <s:f>'05_Annual_Model'!C53</s:f>
-        <s:v/>
+        <s:v>0.7750577243918362</s:v>
       </s:c>
       <s:c r="E28" s="171">
         <s:f>D28-C28</s:f>
-        <s:v/>
+        <s:v>0.29534962701741607</s:v>
       </s:c>
       <s:c r="F28" s="45" t="inlineStr">
         <s:is>
@@ -2674,11 +2674,11 @@
       </s:c>
       <s:c r="C18" s="173">
         <s:f>'05_Annual_Model'!M24</s:f>
-        <s:v>6730600.0</s:v>
+        <s:v>13783630.0</s:v>
       </s:c>
       <s:c r="D18" s="173">
         <s:f>'05_Annual_Model'!M51</s:f>
-        <s:v>16503599.999999998</s:v>
+        <s:v>16403599.99999997</s:v>
       </s:c>
       <s:c r="E18" s="173">
         <s:f>D18-C18</s:f>
@@ -2707,11 +2707,11 @@
       </s:c>
       <s:c r="C19" s="173">
         <s:f>'05_Annual_Model'!C25</s:f>
-        <s:v>2959712.5361993117</s:v>
+        <s:v>7423046.099119451</s:v>
       </s:c>
       <s:c r="D19" s="173">
         <s:f>'05_Annual_Model'!C52</s:f>
-        <s:v>8585493.51572983</s:v>
+        <s:v>8525947.237637723</s:v>
       </s:c>
       <s:c r="E19" s="173">
         <s:f>D19-C19</s:f>
@@ -2740,11 +2740,11 @@
       </s:c>
       <s:c r="C20" s="176">
         <s:f>'05_Annual_Model'!C26</s:f>
-        <s:v>0.2618003333030041</s:v>
+        <s:v>0.4797080973744201</s:v>
       </s:c>
       <s:c r="D20" s="176">
         <s:f>'05_Annual_Model'!C53</s:f>
-        <s:v>0.779970162677768</s:v>
+        <s:v>0.7750577243918362</s:v>
       </s:c>
       <s:c r="E20" s="173">
         <s:f>D20-C20</s:f>
@@ -2773,11 +2773,11 @@
       </s:c>
       <s:c r="C21" s="171">
         <s:f>'05_Annual_Model'!C27</s:f>
-        <s:v>2.901621743798384</s:v>
+        <s:v>4.8943408487314235</s:v>
       </s:c>
       <s:c r="D21" s="171">
         <s:f>'05_Annual_Model'!C54</s:f>
-        <s:v>5.945357970277448</s:v>
+        <s:v>5.917104593998983</s:v>
       </s:c>
       <s:c r="E21" s="171">
         <s:f>D21-C21</s:f>
@@ -3234,7 +3234,7 @@
         </s:is>
       </s:c>
       <s:c r="D6" s="178" t="n">
-        <s:v>5000</s:v>
+        <s:v>4568</s:v>
       </s:c>
       <s:c r="E6" s="45" t="inlineStr">
         <s:is>
@@ -3274,7 +3274,7 @@
         </s:is>
       </s:c>
       <s:c r="D7" s="179" t="n">
-        <s:v>2342300</s:v>
+        <s:v>2600000</s:v>
       </s:c>
       <s:c r="E7" s="45" t="inlineStr">
         <s:is>
@@ -3314,7 +3314,7 @@
         </s:is>
       </s:c>
       <s:c r="D8" s="179" t="n">
-        <s:v>0.5</s:v>
+        <s:v>0.6900001496778997</s:v>
       </s:c>
       <s:c r="E8" s="45" t="inlineStr">
         <s:is>
@@ -3354,7 +3354,7 @@
         </s:is>
       </s:c>
       <s:c r="D9" s="180" t="n">
-        <s:v>204.8318804483188</s:v>
+        <s:v>167.5670046432707</s:v>
       </s:c>
       <s:c r="E9" s="45" t="inlineStr">
         <s:is>
@@ -3474,7 +3474,7 @@
         </s:is>
       </s:c>
       <s:c r="D12" s="178" t="n">
-        <s:v>122</s:v>
+        <s:v>133.536996497373</s:v>
       </s:c>
       <s:c r="E12" s="45" t="inlineStr">
         <s:is>
@@ -3714,7 +3714,7 @@
         </s:is>
       </s:c>
       <s:c r="D18" s="182" t="n">
-        <s:v>707.88</s:v>
+        <s:v>774.8248686514886</s:v>
       </s:c>
       <s:c r="E18" s="50" t="inlineStr">
         <s:is>
@@ -3754,7 +3754,7 @@
         </s:is>
       </s:c>
       <s:c r="D19" s="179" t="n">
-        <s:v>1637000</s:v>
+        <s:v>2342300</s:v>
       </s:c>
       <s:c r="E19" s="45" t="inlineStr">
         <s:is>
@@ -3834,7 +3834,7 @@
         </s:is>
       </s:c>
       <s:c r="D21" s="181" t="n">
-        <s:v>0.5</s:v>
+        <s:v>0.5152196077062881</s:v>
       </s:c>
       <s:c r="E21" s="45" t="inlineStr">
         <s:is>
@@ -3874,7 +3874,7 @@
         </s:is>
       </s:c>
       <s:c r="D22" s="179" t="n">
-        <s:v>81.33333333333333</s:v>
+        <s:v>86.30404640633843</s:v>
       </s:c>
       <s:c r="E22" s="45" t="inlineStr">
         <s:is>
@@ -3914,7 +3914,7 @@
         </s:is>
       </s:c>
       <s:c r="D23" s="179" t="n">
-        <s:v>152500</s:v>
+        <s:v>161820.0870118845</s:v>
       </s:c>
       <s:c r="E23" s="45" t="inlineStr">
         <s:is>
@@ -3954,7 +3954,7 @@
         </s:is>
       </s:c>
       <s:c r="D24" s="179" t="n">
-        <s:v>50833.33333333333</s:v>
+        <s:v>53940.02900396152</s:v>
       </s:c>
       <s:c r="E24" s="45" t="inlineStr">
         <s:is>
@@ -3994,7 +3994,7 @@
         </s:is>
       </s:c>
       <s:c r="D25" s="178" t="n">
-        <s:v>0</s:v>
+        <s:v>0.0</s:v>
       </s:c>
       <s:c r="E25" s="45" t="inlineStr">
         <s:is>
@@ -4115,7 +4115,7 @@
       </s:c>
       <s:c r="D28" s="182">
         <s:f>VLOOKUP($D$48,$A$52:$G$54,3,FALSE)</s:f>
-        <s:v>707.88</s:v>
+        <s:v>774.8248686514886</s:v>
       </s:c>
       <s:c r="E28" s="50" t="inlineStr">
         <s:is>
@@ -4155,7 +4155,7 @@
         </s:is>
       </s:c>
       <s:c r="D29" s="179" t="n">
-        <s:v>2350000</s:v>
+        <s:v>2340000</s:v>
       </s:c>
       <s:c r="E29" s="45" t="inlineStr">
         <s:is>
@@ -4277,7 +4277,7 @@
       </s:c>
       <s:c r="D32" s="179">
         <s:f>VLOOKUP($D$48,$A$52:$G$54,4,FALSE)</s:f>
-        <s:v>18.427500000000002</s:v>
+        <s:v>19.044543199669288</s:v>
       </s:c>
       <s:c r="E32" s="45" t="inlineStr">
         <s:is>
@@ -4318,7 +4318,7 @@
       </s:c>
       <s:c r="D33" s="179">
         <s:f>VLOOKUP($D$48,$A$52:$G$54,5,FALSE)</s:f>
-        <s:v>107493.75000000003</s:v>
+        <s:v>111093.16866473753</s:v>
       </s:c>
       <s:c r="E33" s="45" t="inlineStr">
         <s:is>
@@ -4359,7 +4359,7 @@
       </s:c>
       <s:c r="D34" s="179">
         <s:f>VLOOKUP($D$48,$A$52:$G$54,6,FALSE)</s:f>
-        <s:v>46068.75000000001</s:v>
+        <s:v>47611.357999173226</s:v>
       </s:c>
       <s:c r="E34" s="45" t="inlineStr">
         <s:is>
@@ -4399,7 +4399,7 @@
         </s:is>
       </s:c>
       <s:c r="D35" s="178" t="n">
-        <s:v>0</s:v>
+        <s:v>0.0</s:v>
       </s:c>
       <s:c r="E35" s="45" t="inlineStr">
         <s:is>
@@ -4559,6 +4559,16 @@
         </s:is>
       </s:c>
     </s:row>
+    <s:row r="49">
+      <s:c r="A49" t="inlineStr">
+        <s:is>
+          <s:t>灯杆数量(根)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D49" t="n">
+        <s:v>2345</s:v>
+      </s:c>
+    </s:row>
     <s:row r="50">
       <s:c r="A50" s="183" t="inlineStr">
         <s:is>
@@ -4619,16 +4629,16 @@
         <s:v>0.5869565217391304</s:v>
       </s:c>
       <s:c r="C52" s="186" t="n">
-        <s:v>707.88</s:v>
+        <s:v>774.8248686514886</s:v>
       </s:c>
       <s:c r="D52" s="186" t="n">
-        <s:v>18.4275</s:v>
+        <s:v>19.04454319966929</s:v>
       </s:c>
       <s:c r="E52" s="186" t="n">
-        <s:v>107493.75</s:v>
+        <s:v>111093.1686647375</s:v>
       </s:c>
       <s:c r="F52" s="186" t="n">
-        <s:v>46068.75000000001</s:v>
+        <s:v>47611.35799917323</s:v>
       </s:c>
       <s:c r="G52" s="185" t="inlineStr">
         <s:is>
@@ -4646,16 +4656,16 @@
         <s:v>0.6458333333333333</s:v>
       </s:c>
       <s:c r="C53" s="186" t="n">
-        <s:v>775.9100259740259</s:v>
+        <s:v>849.2885573270861</s:v>
       </s:c>
       <s:c r="D53" s="186" t="n">
-        <s:v>17.855625</s:v>
+        <s:v>18.45351901612237</s:v>
       </s:c>
       <s:c r="E53" s="186" t="n">
-        <s:v>104157.8125</s:v>
+        <s:v>107645.5275940472</s:v>
       </s:c>
       <s:c r="F53" s="186" t="n">
-        <s:v>44639.06250000001</s:v>
+        <s:v>46133.79754030592</s:v>
       </s:c>
       <s:c r="G53" s="185" t="inlineStr">
         <s:is>
@@ -4673,16 +4683,16 @@
         <s:v>0.999</s:v>
       </s:c>
       <s:c r="C54" s="186" t="n">
-        <s:v>671.1070129870129</s:v>
+        <s:v>734.5742261241385</s:v>
       </s:c>
       <s:c r="D54" s="186" t="n">
-        <s:v>5.718750000000001</s:v>
+        <s:v>5.910241835469203</s:v>
       </s:c>
       <s:c r="E54" s="186" t="n">
-        <s:v>33359.37500000001</s:v>
+        <s:v>34476.41070690369</s:v>
       </s:c>
       <s:c r="F54" s="186" t="n">
-        <s:v>14296.875</s:v>
+        <s:v>14775.60458867301</s:v>
       </s:c>
       <s:c r="G54" s="185" t="inlineStr">
         <s:is>
@@ -4707,427 +4717,435 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>现状基准测算｜不改造情形</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="18" t="n"/>
-      <c r="H1" s="18" t="n"/>
-      <c r="I1" s="18" t="n"/>
-      <c r="J1" s="18" t="n"/>
-      <c r="K1" s="18" t="n"/>
-      <c r="L1" s="18" t="n"/>
-      <c r="M1" s="18" t="n"/>
-      <c r="N1" s="18" t="n"/>
-      <c r="O1" s="18" t="n"/>
-      <c r="P1" s="18" t="n"/>
-      <c r="Q1" s="18" t="n"/>
-      <c r="R1" s="18" t="n"/>
-      <c r="S1" s="18" t="n"/>
-      <c r="T1" s="18" t="n"/>
-      <c r="U1" s="18" t="n"/>
-      <c r="V1" s="18" t="n"/>
-      <c r="W1" s="18" t="n"/>
-      <c r="X1" s="18" t="n"/>
-      <c r="Y1" s="18" t="n"/>
-      <c r="Z1" s="18" t="n"/>
-    </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>所有节省额均相对于本页“不改造”基准计算。</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="n"/>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="44" t="inlineStr">
-        <is>
-          <t>项目</t>
-        </is>
-      </c>
-      <c r="B4" s="44" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="C4" s="44" t="inlineStr">
-        <is>
-          <t>公式/口径</t>
-        </is>
-      </c>
-      <c r="D4" s="44" t="inlineStr">
-        <is>
-          <t>计算值</t>
-        </is>
-      </c>
-      <c r="E4" s="44" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F4" s="44" t="inlineStr">
-        <is>
-          <t>校验</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="45" t="inlineStr">
-        <is>
-          <t>灯具数量</t>
-        </is>
-      </c>
-      <c r="B5" s="45" t="inlineStr">
-        <is>
-          <t>盏</t>
-        </is>
-      </c>
-      <c r="C5" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D5" s="187">
-        <f>'02_Inputs'!D6</f>
-        <v/>
-      </c>
-      <c r="E5" s="60" t="str"/>
-      <c r="F5" s="45" t="str"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="45" t="inlineStr">
-        <is>
-          <t>现状单灯功率</t>
-        </is>
-      </c>
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>W/盏</t>
-        </is>
-      </c>
-      <c r="C6" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D6" s="187">
-        <f>'02_Inputs'!D9</f>
-        <v/>
-      </c>
-      <c r="E6" s="60" t="str"/>
-      <c r="F6" s="45" t="str"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="45" t="inlineStr">
-        <is>
-          <t>每日亮灯小时</t>
-        </is>
-      </c>
-      <c r="B7" s="45" t="inlineStr">
-        <is>
-          <t>小时/天</t>
-        </is>
-      </c>
-      <c r="C7" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D7" s="187">
-        <f>'02_Inputs'!D10</f>
-        <v/>
-      </c>
-      <c r="E7" s="60" t="str"/>
-      <c r="F7" s="45" t="str"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="45" t="inlineStr">
-        <is>
-          <t>年运行天数</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>天/年</t>
-        </is>
-      </c>
-      <c r="C8" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D8" s="187">
-        <f>'02_Inputs'!D11</f>
-        <v/>
-      </c>
-      <c r="E8" s="60" t="str"/>
-      <c r="F8" s="45" t="str"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="45" t="inlineStr">
-        <is>
-          <t>年运行小时</t>
-        </is>
-      </c>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>小时/年</t>
-        </is>
-      </c>
-      <c r="C9" s="60" t="inlineStr">
-        <is>
-          <t>每日亮灯小时×年运行天数</t>
-        </is>
-      </c>
-      <c r="D9" s="187">
-        <f>D7*D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="60" t="str"/>
-      <c r="F9" s="45" t="str"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="45" t="inlineStr">
-        <is>
-          <t>现状年用电量</t>
-        </is>
-      </c>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>kWh/年</t>
-        </is>
-      </c>
-      <c r="C10" s="60" t="inlineStr">
-        <is>
-          <t>灯具数量×单灯功率÷1000×年运行小时</t>
-        </is>
-      </c>
-      <c r="D10" s="187">
-        <f>D5*D6/1000*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="60" t="str"/>
-      <c r="F10" s="45" t="str"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="45" t="inlineStr">
-        <is>
-          <t>电价</t>
-        </is>
-      </c>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>元/kWh</t>
-        </is>
-      </c>
-      <c r="C11" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D11" s="188">
-        <f>'02_Inputs'!D8</f>
-        <v/>
-      </c>
-      <c r="E11" s="60" t="str"/>
-      <c r="F11" s="45" t="str"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="45" t="inlineStr">
-        <is>
-          <t>基准年电费</t>
-        </is>
-      </c>
-      <c r="B12" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="C12" s="60" t="inlineStr">
-        <is>
-          <t>现状年用电量×电价</t>
-        </is>
-      </c>
-      <c r="D12" s="189">
-        <f>D10*D11</f>
-        <v/>
-      </c>
-      <c r="E12" s="60" t="str"/>
-      <c r="F12" s="45" t="str"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="45" t="inlineStr">
-        <is>
-          <t>现状运维单价</t>
-        </is>
-      </c>
-      <c r="B13" s="45" t="inlineStr">
-        <is>
-          <t>元/盏/年</t>
-        </is>
-      </c>
-      <c r="C13" s="60" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D13" s="189">
-        <f>'02_Inputs'!D12</f>
-        <v/>
-      </c>
-      <c r="E13" s="60" t="str"/>
-      <c r="F13" s="45" t="str"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="45" t="inlineStr">
-        <is>
-          <t>基准年运维费</t>
-        </is>
-      </c>
-      <c r="B14" s="45" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="C14" s="60" t="inlineStr">
-        <is>
-          <t>灯具数量×现状运维单价</t>
-        </is>
-      </c>
-      <c r="D14" s="189">
-        <f>D5*D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="60" t="str"/>
-      <c r="F14" s="45" t="str"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="79" t="inlineStr">
-        <is>
-          <t>基准年总成本</t>
-        </is>
-      </c>
-      <c r="B15" s="79" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="C15" s="89" t="inlineStr">
-        <is>
-          <t>基准年电费+基准年运维费</t>
-        </is>
-      </c>
-      <c r="D15" s="190">
-        <f>D12+D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="89" t="str"/>
-      <c r="F15" s="79" t="str"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="79" t="inlineStr">
-        <is>
-          <t>业主年度服务费预算</t>
-        </is>
-      </c>
-      <c r="B16" s="79" t="inlineStr">
-        <is>
-          <t>元/年</t>
-        </is>
-      </c>
-      <c r="C16" s="89" t="inlineStr">
-        <is>
-          <t>来自Inputs</t>
-        </is>
-      </c>
-      <c r="D16" s="190">
-        <f>'02_Inputs'!D7</f>
-        <v/>
-      </c>
-      <c r="E16" s="89" t="str"/>
-      <c r="F16" s="79" t="str"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="79" t="inlineStr">
-        <is>
-          <t>10年业主预算总额</t>
-        </is>
-      </c>
-      <c r="B17" s="79" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="C17" s="89" t="inlineStr">
-        <is>
-          <t>年度预算×模型期</t>
-        </is>
-      </c>
-      <c r="D17" s="190">
-        <f>D16*'02_Inputs'!D5</f>
-        <v/>
-      </c>
-      <c r="E17" s="89" t="str"/>
-      <c r="F17" s="79" t="str"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="79" t="inlineStr">
-        <is>
-          <t>10年不改造总成本</t>
-        </is>
-      </c>
-      <c r="B18" s="79" t="inlineStr">
-        <is>
-          <t>元</t>
-        </is>
-      </c>
-      <c r="C18" s="89" t="inlineStr">
-        <is>
-          <t>年度基准总成本合计，考虑增长率</t>
-        </is>
-      </c>
-      <c r="D18" s="190">
-        <f>SUM('05_Annual_Model'!D8:M8)</f>
-        <v/>
-      </c>
-      <c r="E18" s="89" t="str"/>
-      <c r="F18" s="79" t="str"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<s:worksheet xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <s:sheetPr>
+    <s:outlinePr summaryBelow="1" summaryRight="1"/>
+    <s:pageSetUpPr/>
+  </s:sheetPr>
+  <s:dimension ref="A1:Z18"/>
+  <s:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <s:cols>
+    <s:col width="24" customWidth="1" min="1" max="1"/>
+    <s:col width="14" customWidth="1" min="2" max="2"/>
+    <s:col width="46" customWidth="1" min="3" max="3"/>
+    <s:col width="18" customWidth="1" min="4" max="4"/>
+    <s:col width="34" customWidth="1" min="5" max="5"/>
+    <s:col width="16" customWidth="1" min="6" max="6"/>
+  </s:cols>
+  <s:sheetData>
+    <s:row r="1" ht="26" customHeight="1">
+      <s:c r="A1" s="5" t="inlineStr">
+        <s:is>
+          <s:t>现状基准测算｜不改造情形</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B1" s="1" t="n"/>
+      <s:c r="C1" s="1" t="n"/>
+      <s:c r="D1" s="1" t="n"/>
+      <s:c r="E1" s="1" t="n"/>
+      <s:c r="F1" s="1" t="n"/>
+      <s:c r="G1" s="18" t="n"/>
+      <s:c r="H1" s="18" t="n"/>
+      <s:c r="I1" s="18" t="n"/>
+      <s:c r="J1" s="18" t="n"/>
+      <s:c r="K1" s="18" t="n"/>
+      <s:c r="L1" s="18" t="n"/>
+      <s:c r="M1" s="18" t="n"/>
+      <s:c r="N1" s="18" t="n"/>
+      <s:c r="O1" s="18" t="n"/>
+      <s:c r="P1" s="18" t="n"/>
+      <s:c r="Q1" s="18" t="n"/>
+      <s:c r="R1" s="18" t="n"/>
+      <s:c r="S1" s="18" t="n"/>
+      <s:c r="T1" s="18" t="n"/>
+      <s:c r="U1" s="18" t="n"/>
+      <s:c r="V1" s="18" t="n"/>
+      <s:c r="W1" s="18" t="n"/>
+      <s:c r="X1" s="18" t="n"/>
+      <s:c r="Y1" s="18" t="n"/>
+      <s:c r="Z1" s="18" t="n"/>
+    </s:row>
+    <s:row r="2" ht="22" customHeight="1">
+      <s:c r="A2" s="7" t="inlineStr">
+        <s:is>
+          <s:t>所有节省额均相对于本页“不改造”基准计算。</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B2" s="1" t="n"/>
+      <s:c r="C2" s="1" t="n"/>
+      <s:c r="D2" s="1" t="n"/>
+      <s:c r="E2" s="1" t="n"/>
+      <s:c r="F2" s="1" t="n"/>
+    </s:row>
+    <s:row r="4">
+      <s:c r="A4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>项目</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>单位</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>公式/口径</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>计算值</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="E4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>备注</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="F4" s="44" t="inlineStr">
+        <s:is>
+          <s:t>校验</s:t>
+        </s:is>
+      </s:c>
+    </s:row>
+    <s:row r="5">
+      <s:c r="A5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>灯具数量</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C5" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D5" s="187">
+        <s:f>'02_Inputs'!D6</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E5" s="60" t="str"/>
+      <s:c r="F5" s="45" t="inlineStr">
+        <s:is>
+          <s:t>灯杆数量(根)</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="G5">
+        <s:f>'02_Inputs'!D49</s:f>
+        <s:v/>
+      </s:c>
+    </s:row>
+    <s:row r="6">
+      <s:c r="A6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>现状单灯功率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B6" s="45" t="inlineStr">
+        <s:is>
+          <s:t>W/盏</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C6" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D6" s="187">
+        <s:f>'02_Inputs'!D9</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E6" s="60" t="str"/>
+      <s:c r="F6" s="45" t="str"/>
+    </s:row>
+    <s:row r="7">
+      <s:c r="A7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>每日亮灯小时</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B7" s="45" t="inlineStr">
+        <s:is>
+          <s:t>小时/天</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C7" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D7" s="187">
+        <s:f>'02_Inputs'!D10</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E7" s="60" t="str"/>
+      <s:c r="F7" s="45" t="str"/>
+    </s:row>
+    <s:row r="8">
+      <s:c r="A8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年运行天数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B8" s="45" t="inlineStr">
+        <s:is>
+          <s:t>天/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C8" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D8" s="187">
+        <s:f>'02_Inputs'!D11</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E8" s="60" t="str"/>
+      <s:c r="F8" s="45" t="str"/>
+    </s:row>
+    <s:row r="9">
+      <s:c r="A9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>年运行小时</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B9" s="45" t="inlineStr">
+        <s:is>
+          <s:t>小时/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C9" s="60" t="inlineStr">
+        <s:is>
+          <s:t>每日亮灯小时×年运行天数</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D9" s="187">
+        <s:f>D7*D8</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E9" s="60" t="str"/>
+      <s:c r="F9" s="45" t="str"/>
+    </s:row>
+    <s:row r="10">
+      <s:c r="A10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>现状年用电量</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B10" s="45" t="inlineStr">
+        <s:is>
+          <s:t>kWh/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C10" s="60" t="inlineStr">
+        <s:is>
+          <s:t>灯具数量×单灯功率÷1000×年运行小时</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D10" s="187">
+        <s:f>D5*D6/1000*D9</s:f>
+        <s:v>3073266.0</s:v>
+      </s:c>
+      <s:c r="E10" s="60" t="str"/>
+      <s:c r="F10" s="45" t="str"/>
+    </s:row>
+    <s:row r="11">
+      <s:c r="A11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>电价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B11" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/kWh</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C11" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D11" s="188">
+        <s:f>'02_Inputs'!D8</s:f>
+        <s:v>0.6900001496778997</s:v>
+      </s:c>
+      <s:c r="E11" s="60" t="str"/>
+      <s:c r="F11" s="45" t="str"/>
+    </s:row>
+    <s:row r="12">
+      <s:c r="A12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基准年电费</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B12" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C12" s="60" t="inlineStr">
+        <s:is>
+          <s:t>现状年用电量×电价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D12" s="189">
+        <s:f>D10*D11</s:f>
+        <s:v>2120554.0</s:v>
+      </s:c>
+      <s:c r="E12" s="60" t="str"/>
+      <s:c r="F12" s="45" t="str"/>
+    </s:row>
+    <s:row r="13">
+      <s:c r="A13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>现状运维单价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B13" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/盏/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C13" s="60" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D13" s="189">
+        <s:f>'02_Inputs'!D12</s:f>
+        <s:v>133.53699649737302</s:v>
+      </s:c>
+      <s:c r="E13" s="60" t="str"/>
+      <s:c r="F13" s="45" t="str"/>
+    </s:row>
+    <s:row r="14">
+      <s:c r="A14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>基准年运维费</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B14" s="45" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C14" s="60" t="inlineStr">
+        <s:is>
+          <s:t>灯具数量×现状运维单价</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D14" s="189">
+        <s:f>D5*D13</s:f>
+        <s:v>609997.0</s:v>
+      </s:c>
+      <s:c r="E14" s="60" t="str"/>
+      <s:c r="F14" s="45" t="str"/>
+    </s:row>
+    <s:row r="15">
+      <s:c r="A15" s="79" t="inlineStr">
+        <s:is>
+          <s:t>基准年总成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B15" s="79" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C15" s="89" t="inlineStr">
+        <s:is>
+          <s:t>基准年电费+基准年运维费</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D15" s="190">
+        <s:f>D12+D14</s:f>
+        <s:v>2730551.0</s:v>
+      </s:c>
+      <s:c r="E15" s="89" t="str"/>
+      <s:c r="F15" s="79" t="str"/>
+    </s:row>
+    <s:row r="16">
+      <s:c r="A16" s="79" t="inlineStr">
+        <s:is>
+          <s:t>业主年度服务费预算</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B16" s="79" t="inlineStr">
+        <s:is>
+          <s:t>元/年</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C16" s="89" t="inlineStr">
+        <s:is>
+          <s:t>来自Inputs</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D16" s="190">
+        <s:f>'02_Inputs'!D7</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E16" s="89" t="str"/>
+      <s:c r="F16" s="79" t="str"/>
+    </s:row>
+    <s:row r="17">
+      <s:c r="A17" s="79" t="inlineStr">
+        <s:is>
+          <s:t>10年业主预算总额</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B17" s="79" t="inlineStr">
+        <s:is>
+          <s:t>元</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C17" s="89" t="inlineStr">
+        <s:is>
+          <s:t>年度预算×模型期</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D17" s="190">
+        <s:f>D16*'02_Inputs'!D5</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E17" s="89" t="str"/>
+      <s:c r="F17" s="79" t="str"/>
+    </s:row>
+    <s:row r="18">
+      <s:c r="A18" s="79" t="inlineStr">
+        <s:is>
+          <s:t>10年不改造总成本</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="B18" s="79" t="inlineStr">
+        <s:is>
+          <s:t>元</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="C18" s="89" t="inlineStr">
+        <s:is>
+          <s:t>年度基准总成本合计，考虑增长率</s:t>
+        </s:is>
+      </s:c>
+      <s:c r="D18" s="190">
+        <s:f>SUM('05_Annual_Model'!D8:M8)</s:f>
+        <s:v/>
+      </s:c>
+      <s:c r="E18" s="89" t="str"/>
+      <s:c r="F18" s="79" t="str"/>
+    </s:row>
+  </s:sheetData>
+  <s:mergeCells count="2">
+    <s:mergeCell ref="A2:F2"/>
+    <s:mergeCell ref="A1:F1"/>
+  </s:mergeCells>
+  <s:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</s:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7053,7 +7071,7 @@
       </s:c>
       <s:c r="M24" s="195">
         <s:f>L24+M23</s:f>
-        <s:v>6730600.0</s:v>
+        <s:v>13783630.0</s:v>
       </s:c>
     </s:row>
     <s:row r="25">
@@ -7069,7 +7087,7 @@
       </s:c>
       <s:c r="C25" s="196">
         <s:f>NPV('02_Inputs'!$D$13,D23:M23)+C23</s:f>
-        <s:v>2959712.5361993117</s:v>
+        <s:v>7423046.099119451</s:v>
       </s:c>
       <s:c r="D25" s="193" t="n"/>
       <s:c r="E25" s="193" t="n"/>
@@ -7095,7 +7113,7 @@
       </s:c>
       <s:c r="C26" s="197">
         <s:f>IFERROR(IRR(C23:M23),"n/a")</s:f>
-        <s:v>0.2618003333030041</s:v>
+        <s:v>0.4797080973744201</s:v>
       </s:c>
       <s:c r="D26" s="198" t="n"/>
       <s:c r="E26" s="198" t="n"/>
@@ -7121,7 +7139,7 @@
       </s:c>
       <s:c r="C27" s="199">
         <s:f>IF(C12=0,"n/a",SUM(C23:M23)/C12)</s:f>
-        <s:v>2.901621743798384</s:v>
+        <s:v>4.8943408487314235</s:v>
       </s:c>
       <s:c r="D27" s="198" t="n"/>
       <s:c r="E27" s="198" t="n"/>
@@ -7211,43 +7229,43 @@
       </s:c>
       <s:c r="D31" s="193">
         <s:f>D16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="E31" s="193">
         <s:f>E16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="F31" s="193">
         <s:f>F16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="G31" s="193">
         <s:f>G16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="H31" s="193">
         <s:f>H16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="I31" s="193">
         <s:f>I16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="J31" s="193">
         <s:f>J16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="K31" s="193">
         <s:f>K16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="L31" s="193">
         <s:f>L16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
       <s:c r="M31" s="193">
         <s:f>M16*(1-'04_Mode_Params'!$C$10)</s:f>
-        <s:v>1028000.0</s:v>
+        <s:v>1028003.0</s:v>
       </s:c>
     </s:row>
     <s:row r="32">
@@ -7267,43 +7285,43 @@
       </s:c>
       <s:c r="D32" s="193">
         <s:f>D13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="E32" s="193">
         <s:f>E13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="F32" s="193">
         <s:f>F13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="G32" s="193">
         <s:f>G13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="H32" s="193">
         <s:f>H13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="I32" s="193">
         <s:f>I13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="J32" s="193">
         <s:f>J13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="K32" s="193">
         <s:f>K13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="L32" s="193">
         <s:f>L13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
       <s:c r="M32" s="193">
         <s:f>M13</s:f>
-        <s:v>1637000.0</s:v>
+        <s:v>2342300.0</s:v>
       </s:c>
     </s:row>
     <s:row r="33">
@@ -7379,43 +7397,43 @@
       </s:c>
       <s:c r="D34" s="195">
         <s:f>D31+D32+D33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="E34" s="195">
         <s:f>E31+E32+E33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="F34" s="195">
         <s:f>F31+F32+F33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="G34" s="195">
         <s:f>G31+G32+G33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="H34" s="195">
         <s:f>H31+H32+H33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="I34" s="195">
         <s:f>I31+I32+I33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="J34" s="195">
         <s:f>J31+J32+J33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="K34" s="195">
         <s:f>K31+K32+K33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="L34" s="195">
         <s:f>L31+L32+L33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
       <s:c r="M34" s="195">
         <s:f>M31+M32+M33</s:f>
-        <s:v>2665000.0</s:v>
+        <s:v>3370303.0</s:v>
       </s:c>
     </s:row>
     <s:row r="35">
@@ -7435,43 +7453,43 @@
       </s:c>
       <s:c r="D35" s="195">
         <s:f>D8-D34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="E35" s="195">
         <s:f>E8-E34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="F35" s="195">
         <s:f>F8-F34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="G35" s="195">
         <s:f>G8-G34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="H35" s="195">
         <s:f>H8-H34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="I35" s="195">
         <s:f>I8-I34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="J35" s="195">
         <s:f>J8-J34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="K35" s="195">
         <s:f>K8-K34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="L35" s="195">
         <s:f>L8-L34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
       <s:c r="M35" s="195">
         <s:f>M8-M34</s:f>
-        <s:v>1000.0</s:v>
+        <s:v>-639752.0</s:v>
       </s:c>
     </s:row>
     <s:row r="36">
@@ -7637,43 +7655,43 @@
       </s:c>
       <s:c r="D40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(1-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="E40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(2-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="F40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(3-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="G40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(4-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="H40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(5-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="I40" s="193">
         <s:f>MAX(0,('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(6-1))-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="J40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(7-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(7-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="K40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(8-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(8-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="L40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(9-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(9-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="M40" s="193">
         <s:f>MAX(0,MAX((('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(10-1))*0.2),('04_Mode_Params'!$D$6*(1+'02_Inputs'!$D$16)^(10-1))-'02_Inputs'!$D$46)-('02_Inputs'!$D$45/'02_Inputs'!$D$5))</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
     </s:row>
     <s:row r="41">
@@ -8289,7 +8307,7 @@
       </s:c>
       <s:c r="M51" s="195">
         <s:f>L51+M50</s:f>
-        <s:v>16503599.999999998</s:v>
+        <s:v>16403599.99999997</s:v>
       </s:c>
     </s:row>
     <s:row r="52">
@@ -8305,7 +8323,7 @@
       </s:c>
       <s:c r="C52" s="196">
         <s:f>NPV('02_Inputs'!$D$13,D50:M50)+C50</s:f>
-        <s:v>8585493.51572983</s:v>
+        <s:v>8525947.237637723</s:v>
       </s:c>
       <s:c r="D52" s="193" t="n"/>
       <s:c r="E52" s="193" t="n"/>
@@ -8331,7 +8349,7 @@
       </s:c>
       <s:c r="C53" s="197">
         <s:f>IFERROR(IRR(C50:M50),"n/a")</s:f>
-        <s:v>0.779970162677768</s:v>
+        <s:v>0.7750577243918362</s:v>
       </s:c>
       <s:c r="D53" s="198" t="n"/>
       <s:c r="E53" s="198" t="n"/>
@@ -8357,7 +8375,7 @@
       </s:c>
       <s:c r="C54" s="199">
         <s:f>IF(C39=0,"n/a",SUM(C50:M50)/C39)</s:f>
-        <s:v>5.945357970277448</s:v>
+        <s:v>5.917104593998983</s:v>
       </s:c>
       <s:c r="D54" s="198" t="n"/>
       <s:c r="E54" s="198" t="n"/>
@@ -8447,43 +8465,43 @@
       </s:c>
       <s:c r="D58" s="193">
         <s:f>D43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="E58" s="193">
         <s:f>E43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="F58" s="193">
         <s:f>F43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="G58" s="193">
         <s:f>G43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="H58" s="193">
         <s:f>H43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="I58" s="193">
         <s:f>I43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="J58" s="193">
         <s:f>J43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="K58" s="193">
         <s:f>K43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="L58" s="193">
         <s:f>L43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
       <s:c r="M58" s="193">
         <s:f>M43*(1-'04_Mode_Params'!$D$10)</s:f>
-        <s:v>308400.00000000006</s:v>
+        <s:v>318083.10000000003</s:v>
       </s:c>
     </s:row>
     <s:row r="59">
@@ -8503,43 +8521,43 @@
       </s:c>
       <s:c r="D59" s="193">
         <s:f>D40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="E59" s="193">
         <s:f>E40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="F59" s="193">
         <s:f>F40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="G59" s="193">
         <s:f>G40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="H59" s="193">
         <s:f>H40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="I59" s="193">
         <s:f>I40</s:f>
-        <s:v>2350000.0</s:v>
+        <s:v>2340000.0</s:v>
       </s:c>
       <s:c r="J59" s="193">
         <s:f>J40</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="K59" s="193">
         <s:f>K40</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="L59" s="193">
         <s:f>L40</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
       <s:c r="M59" s="193">
         <s:f>M40</s:f>
-        <s:v>2100000.0</s:v>
+        <s:v>2090000.0</s:v>
       </s:c>
     </s:row>
     <s:row r="60">
@@ -8615,43 +8633,43 @@
       </s:c>
       <s:c r="D61" s="195">
         <s:f>D58+D59+D60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="E61" s="195">
         <s:f>E58+E59+E60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="F61" s="195">
         <s:f>F58+F59+F60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="G61" s="195">
         <s:f>G58+G59+G60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="H61" s="195">
         <s:f>H58+H59+H60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="I61" s="195">
         <s:f>I58+I59+I60</s:f>
-        <s:v>2658400.0</s:v>
+        <s:v>2658083.1</s:v>
       </s:c>
       <s:c r="J61" s="195">
         <s:f>J58+J59+J60</s:f>
-        <s:v>2408400.0</s:v>
+        <s:v>2408083.1</s:v>
       </s:c>
       <s:c r="K61" s="195">
         <s:f>K58+K59+K60</s:f>
-        <s:v>2408400.0</s:v>
+        <s:v>2408083.1</s:v>
       </s:c>
       <s:c r="L61" s="195">
         <s:f>L58+L59+L60</s:f>
-        <s:v>2408400.0</s:v>
+        <s:v>2408083.1</s:v>
       </s:c>
       <s:c r="M61" s="195">
         <s:f>M58+M59+M60</s:f>
-        <s:v>2408400.0</s:v>
+        <s:v>2408083.1</s:v>
       </s:c>
     </s:row>
     <s:row r="62">
@@ -8671,43 +8689,43 @@
       </s:c>
       <s:c r="D62" s="195">
         <s:f>D8-D61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="E62" s="195">
         <s:f>E8-E61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="F62" s="195">
         <s:f>F8-F61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="G62" s="195">
         <s:f>G8-G61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="H62" s="195">
         <s:f>H8-H61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="I62" s="195">
         <s:f>I8-I61</s:f>
-        <s:v>7600.0</s:v>
+        <s:v>72467.8999999999</s:v>
       </s:c>
       <s:c r="J62" s="195">
         <s:f>J8-J61</s:f>
-        <s:v>257600.0</s:v>
+        <s:v>322467.8999999999</s:v>
       </s:c>
       <s:c r="K62" s="195">
         <s:f>K8-K61</s:f>
-        <s:v>257600.0</s:v>
+        <s:v>322467.8999999999</s:v>
       </s:c>
       <s:c r="L62" s="195">
         <s:f>L8-L61</s:f>
-        <s:v>257600.0</s:v>
+        <s:v>322467.8999999999</s:v>
       </s:c>
       <s:c r="M62" s="195">
         <s:f>M8-M61</s:f>
-        <s:v>257600.0</s:v>
+        <s:v>322467.8999999999</s:v>
       </s:c>
     </s:row>
     <s:row r="63">
@@ -9232,31 +9250,31 @@
       </s:c>
       <s:c r="B19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.4)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-917600.0</s:v>
+        <s:v>-881781.3999999999</s:v>
       </s:c>
       <s:c r="C19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.45)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-814800.0</s:v>
+        <s:v>-775753.7000000002</s:v>
       </s:c>
       <s:c r="D19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.5)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-712000.0</s:v>
+        <s:v>-637452.0</s:v>
       </s:c>
       <s:c r="E19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.55)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-609200.0</s:v>
+        <s:v>-563698.2999999998</s:v>
       </s:c>
       <s:c r="F19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.6)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-506400.0</s:v>
+        <s:v>-457670.6000000001</s:v>
       </s:c>
       <s:c r="G19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.65)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-403600.0</s:v>
+        <s:v>-351642.8999999999</s:v>
       </s:c>
       <s:c r="H19" s="170">
         <s:f>'03_Baseline'!$D$15-('03_Baseline'!$D$12*(1-0.7)*(1-'04_Mode_Params'!$D$10)+'04_Mode_Params'!$D$6+'02_Inputs'!$D$17)</s:f>
-        <s:v>-300800.0</s:v>
+        <s:v>-245615.2000000002</s:v>
       </s:c>
     </s:row>
     <s:row r="20">

--- a/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
+++ b/Dashboard_LaaS_vs_NYTG/new_models/通用版_能源托管_vs_LaaS_财务模型_v3_逻辑复核版__FILLED_07_Tier07_TailDiscount_WPS.xlsx
@@ -4659,13 +4659,13 @@
         <s:v>849.2885573270861</s:v>
       </s:c>
       <s:c r="D53" s="186" t="n">
-        <s:v>18.45351901612237</s:v>
+        <s:v>19.93107947498967</s:v>
       </s:c>
       <s:c r="E53" s="186" t="n">
-        <s:v>107645.5275940472</s:v>
+        <s:v>116264.6302707731</s:v>
       </s:c>
       <s:c r="F53" s="186" t="n">
-        <s:v>46133.79754030592</s:v>
+        <s:v>49827.69868747418</s:v>
       </s:c>
       <s:c r="G53" s="185" t="inlineStr">
         <s:is>
